--- a/Count.xlsx
+++ b/Count.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2524" uniqueCount="394">
   <si>
     <t>Gen 1</t>
   </si>
@@ -1203,16 +1203,878 @@
     <t>Energy Removal</t>
   </si>
   <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>Input</t>
   </si>
 </sst>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="18">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0066"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7594"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="6">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="96">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF0066"/>
+      <color rgb="FF1B7594"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
 </file>
--- a/Count.xlsx
+++ b/Count.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin\home\ferre\Generations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94C1F4A4-378E-44B8-82E2-3C5F34982F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F36980-2150-4E28-B51F-17A9BBE2341F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FA8DC1D6-4B54-431A-9706-5A86D49164F6}"/>
   </bookViews>
@@ -24,7 +24,6 @@
     <sheet name="Sheet7" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2154,40 +2153,40 @@
   <sheetData>
     <row r="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B1" s="11">
-        <f>B3/$K$3</f>
-        <v>0.12758620689655173</v>
+        <f t="shared" ref="B1:J1" si="0">B3/$K$3</f>
+        <v>0.13220338983050847</v>
       </c>
       <c r="C1" s="11">
-        <f>C3/$K$3</f>
-        <v>0.1310344827586207</v>
+        <f t="shared" si="0"/>
+        <v>0.12881355932203389</v>
       </c>
       <c r="D1" s="11">
-        <f>D3/$K$3</f>
-        <v>0.1310344827586207</v>
+        <f t="shared" si="0"/>
+        <v>0.12881355932203389</v>
       </c>
       <c r="E1" s="11">
-        <f>E3/$K$3</f>
-        <v>0.12758620689655173</v>
+        <f t="shared" si="0"/>
+        <v>0.12542372881355932</v>
       </c>
       <c r="F1" s="11">
-        <f>F3/$K$3</f>
-        <v>0.1310344827586207</v>
+        <f t="shared" si="0"/>
+        <v>0.13898305084745763</v>
       </c>
       <c r="G1" s="11">
-        <f>G3/$K$3</f>
-        <v>9.6551724137931033E-2</v>
+        <f t="shared" si="0"/>
+        <v>9.4915254237288138E-2</v>
       </c>
       <c r="H1" s="11">
-        <f>H3/$K$3</f>
-        <v>0.10344827586206896</v>
+        <f t="shared" si="0"/>
+        <v>0.10169491525423729</v>
       </c>
       <c r="I1" s="11">
-        <f>I3/$K$3</f>
-        <v>9.3103448275862075E-2</v>
+        <f t="shared" si="0"/>
+        <v>9.152542372881356E-2</v>
       </c>
       <c r="J1" s="11">
-        <f>J3/$K$3</f>
-        <v>5.8620689655172413E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.7627118644067797E-2</v>
       </c>
       <c r="K1" s="1"/>
       <c r="M1" s="1"/>
@@ -2197,35 +2196,35 @@
         <v>0.1473170731707317</v>
       </c>
       <c r="P1" s="11">
-        <f t="shared" ref="P1:W1" si="0">P3/$X$3</f>
+        <f t="shared" ref="P1:W1" si="1">P3/$X$3</f>
         <v>9.7560975609756101E-2</v>
       </c>
       <c r="Q1" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.13170731707317074</v>
       </c>
       <c r="R1" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.10439024390243902</v>
       </c>
       <c r="S1" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.15219512195121951</v>
       </c>
       <c r="T1" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.0243902439024397E-2</v>
       </c>
       <c r="U1" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.5853658536585373E-2</v>
       </c>
       <c r="V1" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.3658536585365854E-2</v>
       </c>
       <c r="W1" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.11707317073170732</v>
       </c>
       <c r="X1" s="1"/>
@@ -2297,7 +2296,7 @@
     <row r="3" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
         <f>L10</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3">
         <f>L11</f>
@@ -2313,7 +2312,7 @@
       </c>
       <c r="F3" s="3">
         <f>L14</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G3" s="3">
         <f>L15</f>
@@ -2333,7 +2332,7 @@
       </c>
       <c r="K3" s="3">
         <f>SUM(B3:J3)</f>
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -2383,87 +2382,87 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="11">
-        <f t="shared" ref="O4:W4" si="1">O6/$X$6</f>
+        <f t="shared" ref="O4:W4" si="2">O6/$X$6</f>
         <v>0.14731707317073173</v>
       </c>
       <c r="P4" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.7560975609756101E-2</v>
       </c>
       <c r="Q4" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.13170731707317074</v>
       </c>
       <c r="R4" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.10439024390243903</v>
       </c>
       <c r="S4" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.15219512195121954</v>
       </c>
       <c r="T4" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.0243902439024397E-2</v>
       </c>
       <c r="U4" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.5853658536585373E-2</v>
       </c>
       <c r="V4" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.3658536585365867E-2</v>
       </c>
       <c r="W4" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.11707317073170732</v>
       </c>
       <c r="X4" s="1"/>
     </row>
     <row r="5" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B5" s="11">
-        <f>B7/$K$3</f>
-        <v>0.1206896551724138</v>
+        <f t="shared" ref="B5:L5" si="3">B7/$K$3</f>
+        <v>0.11864406779661017</v>
       </c>
       <c r="C5" s="11">
-        <f>C7/$K$3</f>
-        <v>0.1206896551724138</v>
+        <f t="shared" si="3"/>
+        <v>0.11864406779661017</v>
       </c>
       <c r="D5" s="11">
-        <f>D7/$K$3</f>
-        <v>0.1206896551724138</v>
+        <f t="shared" si="3"/>
+        <v>0.12542372881355932</v>
       </c>
       <c r="E5" s="11">
-        <f>E7/$K$3</f>
-        <v>0.12413793103448276</v>
+        <f t="shared" si="3"/>
+        <v>0.12203389830508475</v>
       </c>
       <c r="F5" s="11">
-        <f>F7/$K$3</f>
-        <v>0.1103448275862069</v>
+        <f t="shared" si="3"/>
+        <v>0.10847457627118644</v>
       </c>
       <c r="G5" s="11">
-        <f>G7/$K$3</f>
-        <v>0.1</v>
+        <f t="shared" si="3"/>
+        <v>9.8305084745762716E-2</v>
       </c>
       <c r="H5" s="11">
-        <f>H7/$K$3</f>
-        <v>0.11724137931034483</v>
+        <f t="shared" si="3"/>
+        <v>0.12542372881355932</v>
       </c>
       <c r="I5" s="11">
-        <f>I7/$K$3</f>
-        <v>6.8965517241379309E-2</v>
+        <f t="shared" si="3"/>
+        <v>6.7796610169491525E-2</v>
       </c>
       <c r="J5" s="11">
-        <f>J7/$K$3</f>
-        <v>0.11724137931034483</v>
+        <f t="shared" si="3"/>
+        <v>0.11525423728813559</v>
       </c>
       <c r="K5" s="11">
-        <f>K7/$K$3</f>
-        <v>0.12413793103448276</v>
+        <f t="shared" si="3"/>
+        <v>0.12203389830508475</v>
       </c>
       <c r="L5" s="11">
-        <f>L7/$K$3</f>
-        <v>2.7586206896551724E-2</v>
+        <f t="shared" si="3"/>
+        <v>2.7118644067796609E-2</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -2557,7 +2556,7 @@
         <v>62.400000000000006</v>
       </c>
       <c r="T6" s="81">
-        <f t="shared" ref="T6:V6" si="2">T3*40%</f>
+        <f t="shared" ref="T6:V6" si="4">T3*40%</f>
         <v>28.8</v>
       </c>
       <c r="U6" s="81">
@@ -2565,7 +2564,7 @@
         <v>35.200000000000003</v>
       </c>
       <c r="V6" s="81">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>38.400000000000006</v>
       </c>
       <c r="W6" s="81">
@@ -2583,28 +2582,28 @@
         <v>35</v>
       </c>
       <c r="C7" s="3">
-        <f t="shared" ref="C7:G7" si="3">D19</f>
+        <f t="shared" ref="C7:G7" si="5">D19</f>
         <v>35</v>
       </c>
       <c r="D7" s="3">
-        <f t="shared" si="3"/>
-        <v>35</v>
+        <f t="shared" si="5"/>
+        <v>37</v>
       </c>
       <c r="E7" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>36</v>
       </c>
       <c r="F7" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>32</v>
       </c>
       <c r="G7" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="H7" s="3">
         <f>I19</f>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I7" s="3">
         <f>J19</f>
@@ -2622,46 +2621,46 @@
       </c>
       <c r="M7" s="3">
         <f>SUM(B7:L7)</f>
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="N7" s="1">
         <f>M7+P14</f>
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="O7" s="11">
         <f>O9/O6</f>
-        <v>0.61258278145695355</v>
+        <v>0.64569536423841056</v>
       </c>
       <c r="P7" s="11">
         <f>P9/P6</f>
         <v>0.95</v>
       </c>
       <c r="Q7" s="11">
-        <f t="shared" ref="Q7:W7" si="4">Q9/Q6</f>
+        <f t="shared" ref="Q7:W7" si="6">Q9/Q6</f>
         <v>0.70370370370370372</v>
       </c>
       <c r="R7" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.86448598130841114</v>
       </c>
       <c r="S7" s="11">
-        <f t="shared" si="4"/>
-        <v>0.60897435897435892</v>
+        <f t="shared" si="6"/>
+        <v>0.65705128205128194</v>
       </c>
       <c r="T7" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.97222222222222221</v>
       </c>
       <c r="U7" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.85227272727272718</v>
       </c>
       <c r="V7" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.70312499999999989</v>
       </c>
       <c r="W7" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.35416666666666669</v>
       </c>
       <c r="X7" s="1"/>
@@ -2679,7 +2678,7 @@
       <c r="M8" s="11"/>
       <c r="N8" s="11">
         <f>M7/N7</f>
-        <v>0.81067961165048541</v>
+        <v>0.81294964028776984</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>0</v>
@@ -2749,7 +2748,7 @@
       <c r="M9" s="1"/>
       <c r="O9" s="81">
         <f>L10</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P9" s="81">
         <f>L11</f>
@@ -2765,7 +2764,7 @@
       </c>
       <c r="S9" s="81">
         <f>L14</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="T9" s="81">
         <f>L15</f>
@@ -2785,14 +2784,14 @@
       </c>
       <c r="X9" s="81">
         <f>SUM(O9:W9)</f>
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Y9" s="65" cm="1">
         <f t="array" ref="Y9:Z9">X9+K7:L7</f>
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="Z9" s="80">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="2:26" x14ac:dyDescent="0.25">
@@ -2806,7 +2805,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" s="3">
         <v>6</v>
@@ -2825,51 +2824,51 @@
         <v>3</v>
       </c>
       <c r="L10" s="3">
-        <f t="shared" ref="L10:L18" si="5">SUM(C10:K10)</f>
-        <v>37</v>
+        <f t="shared" ref="L10:L18" si="7">SUM(C10:K10)</f>
+        <v>39</v>
       </c>
       <c r="M10" s="11">
-        <f t="shared" ref="M10:M18" si="6">L10/$L$19</f>
-        <v>0.12758620689655173</v>
+        <f t="shared" ref="M10:M18" si="8">L10/$L$19</f>
+        <v>0.13220338983050847</v>
       </c>
       <c r="N10" s="80">
         <f>L10-'1.7'!K10</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O10" s="65">
         <f>O6-O9</f>
-        <v>23.400000000000006</v>
+        <v>21.400000000000006</v>
       </c>
       <c r="P10" s="65">
-        <f t="shared" ref="P10:W10" si="7">P6-P9</f>
+        <f t="shared" ref="P10:W10" si="9">P6-P9</f>
         <v>2</v>
       </c>
       <c r="Q10" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
       <c r="R10" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>5.8000000000000043</v>
       </c>
       <c r="S10" s="65">
-        <f t="shared" si="7"/>
-        <v>24.400000000000006</v>
+        <f t="shared" si="9"/>
+        <v>21.400000000000006</v>
       </c>
       <c r="T10" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.80000000000000071</v>
       </c>
       <c r="U10" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>5.2000000000000028</v>
       </c>
       <c r="V10" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>11.400000000000006</v>
       </c>
       <c r="W10" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>31</v>
       </c>
     </row>
@@ -2905,12 +2904,12 @@
         <v>6</v>
       </c>
       <c r="L11" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>38</v>
       </c>
       <c r="M11" s="11">
-        <f t="shared" si="6"/>
-        <v>0.1310344827586207</v>
+        <f t="shared" si="8"/>
+        <v>0.12881355932203389</v>
       </c>
       <c r="N11" s="82">
         <f>L11-'1.7'!K11</f>
@@ -2949,12 +2948,12 @@
         <v>4</v>
       </c>
       <c r="L12" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>38</v>
       </c>
       <c r="M12" s="11">
-        <f t="shared" si="6"/>
-        <v>0.1310344827586207</v>
+        <f t="shared" si="8"/>
+        <v>0.12881355932203389</v>
       </c>
       <c r="N12" s="82">
         <f>L12-'1.7'!K12</f>
@@ -2991,12 +2990,12 @@
         <v>5</v>
       </c>
       <c r="L13" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>37</v>
       </c>
       <c r="M13" s="11">
-        <f t="shared" si="6"/>
-        <v>0.12758620689655173</v>
+        <f t="shared" si="8"/>
+        <v>0.12542372881355932</v>
       </c>
       <c r="N13" s="82">
         <f>L13-'1.7'!K13</f>
@@ -3026,7 +3025,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J14" s="3">
         <v>6</v>
@@ -3035,16 +3034,16 @@
         <v>3</v>
       </c>
       <c r="L14" s="3">
-        <f t="shared" si="5"/>
-        <v>38</v>
+        <f t="shared" si="7"/>
+        <v>41</v>
       </c>
       <c r="M14" s="11">
-        <f t="shared" si="6"/>
-        <v>0.1310344827586207</v>
+        <f t="shared" si="8"/>
+        <v>0.13898305084745763</v>
       </c>
       <c r="N14" s="82">
         <f>L14-'1.7'!K14</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O14" s="80">
         <v>56</v>
@@ -3089,12 +3088,12 @@
         <v>4</v>
       </c>
       <c r="L15" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
       <c r="M15" s="11">
-        <f t="shared" si="6"/>
-        <v>9.6551724137931033E-2</v>
+        <f t="shared" si="8"/>
+        <v>9.4915254237288138E-2</v>
       </c>
       <c r="N15" s="82">
         <f>L15-'1.7'!K15</f>
@@ -3138,12 +3137,12 @@
         <v>4</v>
       </c>
       <c r="L16" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="M16" s="11">
-        <f t="shared" si="6"/>
-        <v>0.10344827586206896</v>
+        <f t="shared" si="8"/>
+        <v>0.10169491525423729</v>
       </c>
       <c r="N16" s="82">
         <f>L16-'1.7'!K16</f>
@@ -3188,12 +3187,12 @@
         <v>3</v>
       </c>
       <c r="L17" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>27</v>
       </c>
       <c r="M17" s="11">
-        <f t="shared" si="6"/>
-        <v>9.3103448275862075E-2</v>
+        <f t="shared" si="8"/>
+        <v>9.152542372881356E-2</v>
       </c>
       <c r="N17" s="82">
         <f>L17-'1.7'!K17</f>
@@ -3236,12 +3235,12 @@
         <v>2</v>
       </c>
       <c r="L18" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="M18" s="11">
-        <f t="shared" si="6"/>
-        <v>5.8620689655172413E-2</v>
+        <f t="shared" si="8"/>
+        <v>5.7627118644067797E-2</v>
       </c>
       <c r="N18" s="82">
         <f>L18-'1.7'!K18</f>
@@ -3257,28 +3256,28 @@
         <v>35</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" ref="D19:H19" si="8">SUM(D10:D18)</f>
+        <f t="shared" ref="D19:H19" si="10">SUM(D10:D18)</f>
         <v>35</v>
       </c>
       <c r="E19" s="3">
-        <f t="shared" si="8"/>
-        <v>35</v>
+        <f t="shared" si="10"/>
+        <v>37</v>
       </c>
       <c r="F19" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>36</v>
       </c>
       <c r="G19" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>32</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>29</v>
       </c>
       <c r="I19" s="3">
         <f>SUM(I10:I18)</f>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J19" s="3">
         <f>SUM(J10:J18)</f>
@@ -3290,47 +3289,47 @@
       </c>
       <c r="L19" s="3">
         <f>SUM(L10:L18)</f>
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="M19" s="1"/>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
       <c r="C20" s="11">
-        <f t="shared" ref="C20:K20" si="9">C19/$L$19</f>
-        <v>0.1206896551724138</v>
+        <f t="shared" ref="C20:K20" si="11">C19/$L$19</f>
+        <v>0.11864406779661017</v>
       </c>
       <c r="D20" s="11">
-        <f t="shared" si="9"/>
-        <v>0.1206896551724138</v>
+        <f t="shared" si="11"/>
+        <v>0.11864406779661017</v>
       </c>
       <c r="E20" s="11">
-        <f t="shared" si="9"/>
-        <v>0.1206896551724138</v>
+        <f t="shared" si="11"/>
+        <v>0.12542372881355932</v>
       </c>
       <c r="F20" s="11">
-        <f t="shared" si="9"/>
-        <v>0.12413793103448276</v>
+        <f t="shared" si="11"/>
+        <v>0.12203389830508475</v>
       </c>
       <c r="G20" s="11">
-        <f t="shared" si="9"/>
-        <v>0.1103448275862069</v>
+        <f t="shared" si="11"/>
+        <v>0.10847457627118644</v>
       </c>
       <c r="H20" s="11">
-        <f t="shared" si="9"/>
-        <v>0.1</v>
+        <f t="shared" si="11"/>
+        <v>9.8305084745762716E-2</v>
       </c>
       <c r="I20" s="11">
         <f>I19/$L$19</f>
-        <v>0.11724137931034483</v>
+        <v>0.12542372881355932</v>
       </c>
       <c r="J20" s="11">
         <f>J19/$L$19</f>
-        <v>6.8965517241379309E-2</v>
+        <v>6.7796610169491525E-2</v>
       </c>
       <c r="K20" s="11">
-        <f t="shared" si="9"/>
-        <v>0.11724137931034483</v>
+        <f t="shared" si="11"/>
+        <v>0.11525423728813559</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -3385,7 +3384,7 @@
       </c>
       <c r="E22" s="65">
         <f>E19-'1.7'!E19</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F22" s="65">
         <f>F19-'1.7'!F19</f>
@@ -3401,7 +3400,7 @@
       </c>
       <c r="I22" s="65">
         <f>I19-'1.7'!I19</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="65">
@@ -3410,7 +3409,7 @@
       </c>
       <c r="L22" s="65">
         <f>SUM(C22:K22)</f>
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.25">

--- a/Count.xlsx
+++ b/Count.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2576" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2709" uniqueCount="458">
   <si>
     <t>Gen 1</t>
   </si>
@@ -1276,6 +1276,126 @@
   </si>
   <si>
     <t>Dudunsparce</t>
+  </si>
+  <si>
+    <t>Lost Isle</t>
+  </si>
+  <si>
+    <t>Grookey</t>
+  </si>
+  <si>
+    <t>Thwackey</t>
+  </si>
+  <si>
+    <t>Rillaboom</t>
+  </si>
+  <si>
+    <t>Snorunt</t>
+  </si>
+  <si>
+    <t>Glalie</t>
+  </si>
+  <si>
+    <t>Froslass</t>
+  </si>
+  <si>
+    <t>Magikarp</t>
+  </si>
+  <si>
+    <t>Gyarados</t>
+  </si>
+  <si>
+    <t>Wimpod</t>
+  </si>
+  <si>
+    <t>Golisopod</t>
+  </si>
+  <si>
+    <t>Clobbopus</t>
+  </si>
+  <si>
+    <t>Grapploct</t>
+  </si>
+  <si>
+    <t>Nacli</t>
+  </si>
+  <si>
+    <t>Naclstack</t>
+  </si>
+  <si>
+    <t>Garganacl</t>
+  </si>
+  <si>
+    <t>Pumpkaboo</t>
+  </si>
+  <si>
+    <t>Gourgeist</t>
+  </si>
+  <si>
+    <t>Golett</t>
+  </si>
+  <si>
+    <t>Golurk</t>
+  </si>
+  <si>
+    <t>Corphish</t>
+  </si>
+  <si>
+    <t>Crawdaunt</t>
+  </si>
+  <si>
+    <t>Sandshrew</t>
+  </si>
+  <si>
+    <t>Sandshlash</t>
+  </si>
+  <si>
+    <t>Roselia</t>
+  </si>
+  <si>
+    <t>Roserade</t>
+  </si>
+  <si>
+    <t>Gothita</t>
+  </si>
+  <si>
+    <t>Gothorita</t>
+  </si>
+  <si>
+    <t>Gothitelle</t>
+  </si>
+  <si>
+    <t>Skarmory</t>
+  </si>
+  <si>
+    <t>Joltik</t>
+  </si>
+  <si>
+    <t>Galvantula</t>
+  </si>
+  <si>
+    <t>Regice</t>
+  </si>
+  <si>
+    <t>Regirock</t>
+  </si>
+  <si>
+    <t>Registeel</t>
+  </si>
+  <si>
+    <t>Regidrago</t>
+  </si>
+  <si>
+    <t>Metal Pokemon</t>
+  </si>
+  <si>
+    <t>Drakloak</t>
+  </si>
+  <si>
+    <t>Dreepy</t>
+  </si>
+  <si>
+    <t>Dragapult</t>
   </si>
 </sst>
 </file>
@@ -1345,7 +1465,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1454,6 +1574,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF808080"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -1544,7 +1670,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1805,6 +1931,93 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1842,12 +2055,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1859,6 +2066,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF808080"/>
       <color rgb="FFFF0066"/>
       <color rgb="FF1B7594"/>
     </mruColors>
@@ -2187,4 +2395,6199 @@
     </a:ext>
   </a:extLst>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:Y36"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="10" style="74"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B1" s="11">
+        <f>B3/$K$3</f>
+        <v>0.12781954887218044</v>
+      </c>
+      <c r="C1" s="11">
+        <f t="shared" ref="C1:I1" si="0">C3/$K$3</f>
+        <v>0.12030075187969924</v>
+      </c>
+      <c r="D1" s="11">
+        <f t="shared" si="0"/>
+        <v>0.13909774436090225</v>
+      </c>
+      <c r="E1" s="11">
+        <f t="shared" si="0"/>
+        <v>0.12781954887218044</v>
+      </c>
+      <c r="F1" s="11">
+        <f t="shared" si="0"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="G1" s="11">
+        <f t="shared" si="0"/>
+        <v>8.646616541353383E-2</v>
+      </c>
+      <c r="H1" s="11">
+        <f t="shared" si="0"/>
+        <v>0.11278195488721804</v>
+      </c>
+      <c r="I1" s="11">
+        <f t="shared" si="0"/>
+        <v>0.10150375939849623</v>
+      </c>
+      <c r="J1" s="11">
+        <f>J3/$K$3</f>
+        <v>4.1353383458646614E-2</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="11">
+        <f>N3/$W$3</f>
+        <v>0.1473170731707317</v>
+      </c>
+      <c r="O1" s="11">
+        <f t="shared" ref="O1:V1" si="1">O3/$W$3</f>
+        <v>9.7560975609756101E-2</v>
+      </c>
+      <c r="P1" s="11">
+        <f t="shared" si="1"/>
+        <v>0.13170731707317074</v>
+      </c>
+      <c r="Q1" s="11">
+        <f t="shared" si="1"/>
+        <v>0.10439024390243902</v>
+      </c>
+      <c r="R1" s="11">
+        <f t="shared" si="1"/>
+        <v>0.15219512195121951</v>
+      </c>
+      <c r="S1" s="11">
+        <f t="shared" si="1"/>
+        <v>7.0243902439024397E-2</v>
+      </c>
+      <c r="T1" s="11">
+        <f t="shared" si="1"/>
+        <v>8.5853658536585373E-2</v>
+      </c>
+      <c r="U1" s="11">
+        <f t="shared" si="1"/>
+        <v>9.3658536585365854E-2</v>
+      </c>
+      <c r="V1" s="11">
+        <f t="shared" si="1"/>
+        <v>0.11707317073170732</v>
+      </c>
+      <c r="W1" s="1"/>
+    </row>
+    <row r="2" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B3" s="3">
+        <f>K10</f>
+        <v>34</v>
+      </c>
+      <c r="C3" s="3">
+        <f>K11</f>
+        <v>32</v>
+      </c>
+      <c r="D3" s="3">
+        <f>K12</f>
+        <v>37</v>
+      </c>
+      <c r="E3" s="3">
+        <f>K13</f>
+        <v>34</v>
+      </c>
+      <c r="F3" s="3">
+        <f>K14</f>
+        <v>38</v>
+      </c>
+      <c r="G3" s="3">
+        <f>K15</f>
+        <v>23</v>
+      </c>
+      <c r="H3" s="3">
+        <f>K16</f>
+        <v>30</v>
+      </c>
+      <c r="I3" s="3">
+        <f>K17</f>
+        <v>27</v>
+      </c>
+      <c r="J3" s="3">
+        <f>K18</f>
+        <v>11</v>
+      </c>
+      <c r="K3" s="3">
+        <f>SUM(B3:J3)</f>
+        <v>266</v>
+      </c>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="3">
+        <v>151</v>
+      </c>
+      <c r="O3" s="3">
+        <v>100</v>
+      </c>
+      <c r="P3" s="3">
+        <v>135</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>107</v>
+      </c>
+      <c r="R3" s="3">
+        <v>156</v>
+      </c>
+      <c r="S3" s="3">
+        <v>72</v>
+      </c>
+      <c r="T3" s="3">
+        <v>88</v>
+      </c>
+      <c r="U3" s="3">
+        <v>96</v>
+      </c>
+      <c r="V3" s="3">
+        <v>120</v>
+      </c>
+      <c r="W3" s="3">
+        <f>SUM(N3:V3)</f>
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="4" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="11">
+        <f t="shared" ref="N4:V4" si="2">N6/$W$6</f>
+        <v>0.14731707317073173</v>
+      </c>
+      <c r="O4" s="11">
+        <f t="shared" si="2"/>
+        <v>9.7560975609756101E-2</v>
+      </c>
+      <c r="P4" s="11">
+        <f t="shared" si="2"/>
+        <v>0.13170731707317074</v>
+      </c>
+      <c r="Q4" s="11">
+        <f t="shared" si="2"/>
+        <v>0.10439024390243903</v>
+      </c>
+      <c r="R4" s="11">
+        <f t="shared" si="2"/>
+        <v>0.15219512195121954</v>
+      </c>
+      <c r="S4" s="11">
+        <f t="shared" si="2"/>
+        <v>7.0243902439024397E-2</v>
+      </c>
+      <c r="T4" s="11">
+        <f t="shared" si="2"/>
+        <v>8.5853658536585373E-2</v>
+      </c>
+      <c r="U4" s="11">
+        <f t="shared" si="2"/>
+        <v>9.3658536585365867E-2</v>
+      </c>
+      <c r="V4" s="11">
+        <f t="shared" si="2"/>
+        <v>0.11707317073170732</v>
+      </c>
+      <c r="W4" s="1"/>
+    </row>
+    <row r="5" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B5" s="11">
+        <f t="shared" ref="B5:G5" si="3">B7/$K$3</f>
+        <v>0.13533834586466165</v>
+      </c>
+      <c r="C5" s="11">
+        <f t="shared" si="3"/>
+        <v>0.12030075187969924</v>
+      </c>
+      <c r="D5" s="11">
+        <f t="shared" si="3"/>
+        <v>0.12406015037593984</v>
+      </c>
+      <c r="E5" s="11">
+        <f t="shared" si="3"/>
+        <v>0.12406015037593984</v>
+      </c>
+      <c r="F5" s="11">
+        <f t="shared" si="3"/>
+        <v>0.12781954887218044</v>
+      </c>
+      <c r="G5" s="11">
+        <f t="shared" si="3"/>
+        <v>0.12406015037593984</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" ref="H5" si="4">H7/$K$3</f>
+        <v>0.12030075187969924</v>
+      </c>
+      <c r="I5" s="11">
+        <f>I7/$K$3</f>
+        <v>0.12406015037593984</v>
+      </c>
+      <c r="J5" s="11">
+        <f>J7/$K$3</f>
+        <v>0.13533834586466165</v>
+      </c>
+      <c r="K5" s="11">
+        <f>K7/$K$3</f>
+        <v>3.007518796992481E-2</v>
+      </c>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="70" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" s="1"/>
+      <c r="N6" s="81">
+        <f>N3*40%</f>
+        <v>60.400000000000006</v>
+      </c>
+      <c r="O6" s="81">
+        <f>O3*40%</f>
+        <v>40</v>
+      </c>
+      <c r="P6" s="81">
+        <f>P3*40%</f>
+        <v>54</v>
+      </c>
+      <c r="Q6" s="81">
+        <f>Q3*40%</f>
+        <v>42.800000000000004</v>
+      </c>
+      <c r="R6" s="81">
+        <f>R3*40%</f>
+        <v>62.400000000000006</v>
+      </c>
+      <c r="S6" s="81">
+        <f t="shared" ref="S6:U6" si="5">S3*40%</f>
+        <v>28.8</v>
+      </c>
+      <c r="T6" s="81">
+        <f>T3*40%</f>
+        <v>35.200000000000003</v>
+      </c>
+      <c r="U6" s="81">
+        <f t="shared" si="5"/>
+        <v>38.400000000000006</v>
+      </c>
+      <c r="V6" s="81">
+        <f>V3*40%</f>
+        <v>48</v>
+      </c>
+      <c r="W6" s="81">
+        <f>SUM(N6:V6)</f>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="7" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B7" s="3">
+        <f>C19</f>
+        <v>36</v>
+      </c>
+      <c r="C7" s="3">
+        <f t="shared" ref="C7:H7" si="6">D19</f>
+        <v>32</v>
+      </c>
+      <c r="D7" s="3">
+        <f t="shared" si="6"/>
+        <v>33</v>
+      </c>
+      <c r="E7" s="3">
+        <f t="shared" si="6"/>
+        <v>33</v>
+      </c>
+      <c r="F7" s="3">
+        <f t="shared" si="6"/>
+        <v>34</v>
+      </c>
+      <c r="G7" s="3">
+        <f t="shared" si="6"/>
+        <v>33</v>
+      </c>
+      <c r="H7" s="3">
+        <f t="shared" si="6"/>
+        <v>32</v>
+      </c>
+      <c r="I7" s="3">
+        <f>J19</f>
+        <v>33</v>
+      </c>
+      <c r="J7" s="3">
+        <v>36</v>
+      </c>
+      <c r="K7" s="3">
+        <v>8</v>
+      </c>
+      <c r="L7" s="3">
+        <f>SUM(B7:K7)</f>
+        <v>310</v>
+      </c>
+      <c r="M7" s="1"/>
+      <c r="N7" s="11">
+        <f>N9/N6</f>
+        <v>0.5629139072847682</v>
+      </c>
+      <c r="O7" s="11">
+        <f>O9/O6</f>
+        <v>0.8</v>
+      </c>
+      <c r="P7" s="11">
+        <f t="shared" ref="P7:V7" si="7">P9/P6</f>
+        <v>0.68518518518518523</v>
+      </c>
+      <c r="Q7" s="11">
+        <f t="shared" si="7"/>
+        <v>0.79439252336448585</v>
+      </c>
+      <c r="R7" s="11">
+        <f t="shared" si="7"/>
+        <v>0.60897435897435892</v>
+      </c>
+      <c r="S7" s="11">
+        <f t="shared" si="7"/>
+        <v>0.79861111111111105</v>
+      </c>
+      <c r="T7" s="11">
+        <f t="shared" si="7"/>
+        <v>0.85227272727272718</v>
+      </c>
+      <c r="U7" s="11">
+        <f t="shared" si="7"/>
+        <v>0.70312499999999989</v>
+      </c>
+      <c r="V7" s="11">
+        <f t="shared" si="7"/>
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="W7" s="1"/>
+    </row>
+    <row r="8" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="N8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="70" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="1"/>
+      <c r="N9" s="81">
+        <f>K10</f>
+        <v>34</v>
+      </c>
+      <c r="O9" s="81">
+        <f>K11</f>
+        <v>32</v>
+      </c>
+      <c r="P9" s="81">
+        <f>K12</f>
+        <v>37</v>
+      </c>
+      <c r="Q9" s="81">
+        <f>K13</f>
+        <v>34</v>
+      </c>
+      <c r="R9" s="81">
+        <f>K14</f>
+        <v>38</v>
+      </c>
+      <c r="S9" s="81">
+        <f>K15</f>
+        <v>23</v>
+      </c>
+      <c r="T9" s="81">
+        <f>K16</f>
+        <v>30</v>
+      </c>
+      <c r="U9" s="81">
+        <f>K17</f>
+        <v>27</v>
+      </c>
+      <c r="V9" s="81">
+        <f>K18</f>
+        <v>11</v>
+      </c>
+      <c r="W9" s="81">
+        <f>SUM(N9:V9)</f>
+        <v>266</v>
+      </c>
+      <c r="X9" s="65" cm="1">
+        <f t="array" ref="X9:Y9">W9+J7:K7</f>
+        <v>302</v>
+      </c>
+      <c r="Y9" s="74">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="10" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7</v>
+      </c>
+      <c r="F10" s="3">
+        <v>6</v>
+      </c>
+      <c r="G10" s="3">
+        <v>4</v>
+      </c>
+      <c r="H10" s="3">
+        <v>5</v>
+      </c>
+      <c r="I10" s="3">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3">
+        <f t="shared" ref="K10:K18" si="8">SUM(C10:J10)</f>
+        <v>34</v>
+      </c>
+      <c r="L10" s="11">
+        <f t="shared" ref="L10:L18" si="9">K10/$K$19</f>
+        <v>0.12781954887218044</v>
+      </c>
+      <c r="S10" s="65"/>
+    </row>
+    <row r="11" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3">
+        <v>4</v>
+      </c>
+      <c r="D11" s="3">
+        <v>5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>3</v>
+      </c>
+      <c r="G11" s="3">
+        <v>6</v>
+      </c>
+      <c r="H11" s="3">
+        <v>2</v>
+      </c>
+      <c r="I11" s="3">
+        <v>4</v>
+      </c>
+      <c r="J11" s="3">
+        <v>6</v>
+      </c>
+      <c r="K11" s="3">
+        <f t="shared" si="8"/>
+        <v>32</v>
+      </c>
+      <c r="L11" s="11">
+        <f t="shared" si="9"/>
+        <v>0.12030075187969924</v>
+      </c>
+    </row>
+    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3">
+        <v>7</v>
+      </c>
+      <c r="D12" s="3">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>6</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
+        <v>2</v>
+      </c>
+      <c r="J12" s="3">
+        <v>4</v>
+      </c>
+      <c r="K12" s="3">
+        <f t="shared" si="8"/>
+        <v>37</v>
+      </c>
+      <c r="L12" s="11">
+        <f t="shared" si="9"/>
+        <v>0.13909774436090225</v>
+      </c>
+    </row>
+    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="3">
+        <v>6</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3</v>
+      </c>
+      <c r="F13" s="3">
+        <v>5</v>
+      </c>
+      <c r="G13" s="3">
+        <v>3</v>
+      </c>
+      <c r="H13" s="3">
+        <v>4</v>
+      </c>
+      <c r="I13" s="3">
+        <v>7</v>
+      </c>
+      <c r="J13" s="3">
+        <v>5</v>
+      </c>
+      <c r="K13" s="3">
+        <f t="shared" si="8"/>
+        <v>34</v>
+      </c>
+      <c r="L13" s="11">
+        <f t="shared" si="9"/>
+        <v>0.12781954887218044</v>
+      </c>
+    </row>
+    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="3">
+        <v>6</v>
+      </c>
+      <c r="D14" s="3">
+        <v>9</v>
+      </c>
+      <c r="E14" s="3">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>6</v>
+      </c>
+      <c r="G14" s="3">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2</v>
+      </c>
+      <c r="I14" s="3">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
+        <f t="shared" si="8"/>
+        <v>38</v>
+      </c>
+      <c r="L14" s="11">
+        <f t="shared" si="9"/>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="15" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2</v>
+      </c>
+      <c r="G15" s="3">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3">
+        <v>2</v>
+      </c>
+      <c r="J15" s="3">
+        <v>4</v>
+      </c>
+      <c r="K15" s="3">
+        <f t="shared" si="8"/>
+        <v>23</v>
+      </c>
+      <c r="L15" s="11">
+        <f t="shared" si="9"/>
+        <v>8.646616541353383E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="3">
+        <v>6</v>
+      </c>
+      <c r="D16" s="3">
+        <v>3</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3</v>
+      </c>
+      <c r="F16" s="3">
+        <v>4</v>
+      </c>
+      <c r="G16" s="3">
+        <v>6</v>
+      </c>
+      <c r="H16" s="3">
+        <v>3</v>
+      </c>
+      <c r="I16" s="3">
+        <v>1</v>
+      </c>
+      <c r="J16" s="3">
+        <v>4</v>
+      </c>
+      <c r="K16" s="3">
+        <f t="shared" si="8"/>
+        <v>30</v>
+      </c>
+      <c r="L16" s="11">
+        <f t="shared" si="9"/>
+        <v>0.11278195488721804</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="3">
+        <v>3</v>
+      </c>
+      <c r="D17" s="3">
+        <v>2</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3">
+        <v>6</v>
+      </c>
+      <c r="H17" s="3">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3">
+        <v>4</v>
+      </c>
+      <c r="J17" s="3">
+        <v>3</v>
+      </c>
+      <c r="K17" s="3">
+        <f t="shared" si="8"/>
+        <v>27</v>
+      </c>
+      <c r="L17" s="11">
+        <f t="shared" si="9"/>
+        <v>0.10150375939849623</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3">
+        <v>2</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1</v>
+      </c>
+      <c r="K18" s="3">
+        <f t="shared" si="8"/>
+        <v>11</v>
+      </c>
+      <c r="L18" s="11">
+        <f t="shared" si="9"/>
+        <v>4.1353383458646614E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="3">
+        <f>SUM(C10:C18)</f>
+        <v>36</v>
+      </c>
+      <c r="D19" s="3">
+        <f t="shared" ref="D19:H19" si="10">SUM(D10:D18)</f>
+        <v>32</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="10"/>
+        <v>33</v>
+      </c>
+      <c r="F19" s="3">
+        <f t="shared" si="10"/>
+        <v>33</v>
+      </c>
+      <c r="G19" s="3">
+        <f t="shared" si="10"/>
+        <v>34</v>
+      </c>
+      <c r="H19" s="3">
+        <f t="shared" si="10"/>
+        <v>33</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" ref="I19" si="11">SUM(I10:I18)</f>
+        <v>32</v>
+      </c>
+      <c r="J19" s="3">
+        <f>SUM(J10:J18)</f>
+        <v>33</v>
+      </c>
+      <c r="K19" s="3">
+        <f>SUM(K10:K18)</f>
+        <v>266</v>
+      </c>
+      <c r="L19" s="1"/>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B20" s="1"/>
+      <c r="C20" s="11">
+        <f t="shared" ref="C20:J20" si="12">C19/$K$19</f>
+        <v>0.13533834586466165</v>
+      </c>
+      <c r="D20" s="11">
+        <f t="shared" si="12"/>
+        <v>0.12030075187969924</v>
+      </c>
+      <c r="E20" s="11">
+        <f t="shared" si="12"/>
+        <v>0.12406015037593984</v>
+      </c>
+      <c r="F20" s="11">
+        <f t="shared" si="12"/>
+        <v>0.12406015037593984</v>
+      </c>
+      <c r="G20" s="11">
+        <f t="shared" si="12"/>
+        <v>0.12781954887218044</v>
+      </c>
+      <c r="H20" s="11">
+        <f t="shared" si="12"/>
+        <v>0.12406015037593984</v>
+      </c>
+      <c r="I20" s="11">
+        <f t="shared" si="12"/>
+        <v>0.12030075187969924</v>
+      </c>
+      <c r="J20" s="11">
+        <f t="shared" si="12"/>
+        <v>0.12406015037593984</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="O27" s="74" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="O28" s="74">
+        <v>31</v>
+      </c>
+      <c r="P28" s="74">
+        <v>255</v>
+      </c>
+      <c r="Q28" s="65"/>
+      <c r="R28" s="65"/>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="O29" s="62">
+        <v>30</v>
+      </c>
+      <c r="P29" s="66">
+        <f>(O29*255)/31</f>
+        <v>246.7741935483871</v>
+      </c>
+      <c r="R29" s="74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="O30" s="63">
+        <v>27</v>
+      </c>
+      <c r="P30" s="67">
+        <f>(O30*255)/31</f>
+        <v>222.09677419354838</v>
+      </c>
+      <c r="R30" s="74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="O31" s="64">
+        <v>24</v>
+      </c>
+      <c r="P31" s="68">
+        <f>(O31*255)/31</f>
+        <v>197.41935483870967</v>
+      </c>
+      <c r="R31" s="74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="P32" s="74" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="33" spans="15:16" x14ac:dyDescent="0.25">
+      <c r="O33" s="74">
+        <v>255</v>
+      </c>
+      <c r="P33" s="74">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="15:16" x14ac:dyDescent="0.25">
+      <c r="O34" s="66">
+        <f>(P34*31)/255</f>
+        <v>30.149019607843137</v>
+      </c>
+      <c r="P34" s="66">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="35" spans="15:16" x14ac:dyDescent="0.25">
+      <c r="O35" s="67">
+        <f>(P35*31)/255</f>
+        <v>33.79607843137255</v>
+      </c>
+      <c r="P35" s="67">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="36" spans="15:16" x14ac:dyDescent="0.25">
+      <c r="O36" s="68">
+        <f>(P36*31)/255</f>
+        <v>0</v>
+      </c>
+      <c r="P36" s="68">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00D3A953-7727-4F00-A7CC-D89B6553E3AF}">
+  <dimension ref="B1:T19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B1" s="11">
+        <f>B3/$K$3</f>
+        <v>0.107981220657277</v>
+      </c>
+      <c r="C1" s="11">
+        <f t="shared" ref="C1:J1" si="0">C3/$K$3</f>
+        <v>0.13145539906103287</v>
+      </c>
+      <c r="D1" s="11">
+        <f t="shared" si="0"/>
+        <v>0.14553990610328638</v>
+      </c>
+      <c r="E1" s="11">
+        <f t="shared" si="0"/>
+        <v>0.11737089201877934</v>
+      </c>
+      <c r="F1" s="11">
+        <f t="shared" si="0"/>
+        <v>0.15492957746478872</v>
+      </c>
+      <c r="G1" s="11">
+        <f t="shared" si="0"/>
+        <v>9.8591549295774641E-2</v>
+      </c>
+      <c r="H1" s="11">
+        <f t="shared" si="0"/>
+        <v>0.10328638497652583</v>
+      </c>
+      <c r="I1" s="11">
+        <f t="shared" si="0"/>
+        <v>0.12206572769953052</v>
+      </c>
+      <c r="J1" s="11">
+        <f t="shared" si="0"/>
+        <v>1.8779342723004695E-2</v>
+      </c>
+    </row>
+    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B3" s="3">
+        <v>23</v>
+      </c>
+      <c r="C3" s="3">
+        <v>28</v>
+      </c>
+      <c r="D3" s="3">
+        <v>31</v>
+      </c>
+      <c r="E3" s="3">
+        <v>25</v>
+      </c>
+      <c r="F3" s="3">
+        <v>33</v>
+      </c>
+      <c r="G3" s="3">
+        <v>21</v>
+      </c>
+      <c r="H3" s="3">
+        <v>22</v>
+      </c>
+      <c r="I3" s="3">
+        <v>26</v>
+      </c>
+      <c r="J3" s="3">
+        <v>4</v>
+      </c>
+      <c r="K3" s="3">
+        <f>SUM(B3:J3)</f>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="J4"/>
+    </row>
+    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B5" s="11">
+        <f t="shared" ref="B5:H5" si="1">B7/$K$3</f>
+        <v>0.18779342723004694</v>
+      </c>
+      <c r="C5" s="11">
+        <f t="shared" si="1"/>
+        <v>0.13145539906103287</v>
+      </c>
+      <c r="D5" s="11">
+        <f t="shared" si="1"/>
+        <v>0.14553990610328638</v>
+      </c>
+      <c r="E5" s="11">
+        <f t="shared" si="1"/>
+        <v>0.12676056338028169</v>
+      </c>
+      <c r="F5" s="11">
+        <f t="shared" si="1"/>
+        <v>0.12676056338028169</v>
+      </c>
+      <c r="G5" s="11">
+        <f t="shared" si="1"/>
+        <v>0.12676056338028169</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="1"/>
+        <v>0.15492957746478872</v>
+      </c>
+      <c r="I5"/>
+    </row>
+    <row r="6" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="B6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B7" s="3">
+        <v>40</v>
+      </c>
+      <c r="C7" s="3">
+        <v>28</v>
+      </c>
+      <c r="D7" s="3">
+        <v>31</v>
+      </c>
+      <c r="E7" s="3">
+        <v>27</v>
+      </c>
+      <c r="F7" s="3">
+        <v>27</v>
+      </c>
+      <c r="G7" s="3">
+        <v>27</v>
+      </c>
+      <c r="H7" s="3">
+        <v>33</v>
+      </c>
+      <c r="I7" s="3">
+        <f>SUM(B7:H7)</f>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="I8" s="1">
+        <f>254-I7</f>
+        <v>41</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="I9" s="1">
+        <f>I8-7</f>
+        <v>34</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
+        <v>2</v>
+      </c>
+      <c r="M9" s="3">
+        <v>2</v>
+      </c>
+      <c r="N9" s="3">
+        <v>7</v>
+      </c>
+      <c r="O9" s="3">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>1</v>
+      </c>
+      <c r="R9" s="3">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3">
+        <f>SUM(L9:R9)</f>
+        <v>23</v>
+      </c>
+      <c r="T9" s="11">
+        <f>S9/$S$18</f>
+        <v>0.107981220657277</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="K10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="3">
+        <v>6</v>
+      </c>
+      <c r="M10" s="3">
+        <v>6</v>
+      </c>
+      <c r="N10" s="3">
+        <v>2</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1</v>
+      </c>
+      <c r="P10" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3">
+        <v>6</v>
+      </c>
+      <c r="S10" s="3">
+        <f t="shared" ref="S10:S16" si="2">SUM(L10:R10)</f>
+        <v>28</v>
+      </c>
+      <c r="T10" s="11">
+        <f t="shared" ref="T10:T17" si="3">S10/$S$18</f>
+        <v>0.13145539906103287</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="K11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="L11" s="3">
+        <v>9</v>
+      </c>
+      <c r="M11" s="3">
+        <v>5</v>
+      </c>
+      <c r="N11" s="3">
+        <v>3</v>
+      </c>
+      <c r="O11" s="3">
+        <v>2</v>
+      </c>
+      <c r="P11" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>5</v>
+      </c>
+      <c r="R11" s="3">
+        <v>4</v>
+      </c>
+      <c r="S11" s="3">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="T11" s="11">
+        <f t="shared" si="3"/>
+        <v>0.14553990610328638</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="K12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3">
+        <v>1</v>
+      </c>
+      <c r="N12" s="3">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>6</v>
+      </c>
+      <c r="R12" s="3">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="T12" s="11">
+        <f t="shared" si="3"/>
+        <v>0.11737089201877934</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="K13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" s="3">
+        <v>6</v>
+      </c>
+      <c r="M13" s="3">
+        <v>6</v>
+      </c>
+      <c r="N13" s="3">
+        <v>4</v>
+      </c>
+      <c r="O13" s="3">
+        <v>6</v>
+      </c>
+      <c r="P13" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>5</v>
+      </c>
+      <c r="R13" s="3">
+        <v>3</v>
+      </c>
+      <c r="S13" s="3">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="T13" s="11">
+        <f t="shared" si="3"/>
+        <v>0.15492957746478872</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="K14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
+        <v>2</v>
+      </c>
+      <c r="M14" s="3">
+        <v>2</v>
+      </c>
+      <c r="N14" s="3">
+        <v>7</v>
+      </c>
+      <c r="O14" s="3">
+        <v>2</v>
+      </c>
+      <c r="P14" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>2</v>
+      </c>
+      <c r="R14" s="3">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="T14" s="11">
+        <f t="shared" si="3"/>
+        <v>9.8591549295774641E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="K15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L15" s="3">
+        <v>7</v>
+      </c>
+      <c r="M15" s="3">
+        <v>1</v>
+      </c>
+      <c r="N15" s="3">
+        <v>2</v>
+      </c>
+      <c r="O15" s="3">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>2</v>
+      </c>
+      <c r="R15" s="3">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="T15" s="11">
+        <f t="shared" si="3"/>
+        <v>0.10328638497652583</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="K16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L16" s="3">
+        <v>4</v>
+      </c>
+      <c r="M16" s="3">
+        <v>2</v>
+      </c>
+      <c r="N16" s="3">
+        <v>3</v>
+      </c>
+      <c r="O16" s="3">
+        <v>5</v>
+      </c>
+      <c r="P16" s="3">
+        <v>6</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>2</v>
+      </c>
+      <c r="R16" s="3">
+        <v>4</v>
+      </c>
+      <c r="S16" s="3">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="T16" s="11">
+        <f t="shared" si="3"/>
+        <v>0.12206572769953052</v>
+      </c>
+    </row>
+    <row r="17" spans="11:20" x14ac:dyDescent="0.25">
+      <c r="K17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+      <c r="R17" s="3">
+        <v>1</v>
+      </c>
+      <c r="S17" s="3">
+        <f>SUM(L17:R17)</f>
+        <v>4</v>
+      </c>
+      <c r="T17" s="11">
+        <f t="shared" si="3"/>
+        <v>1.8779342723004695E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="11:20" x14ac:dyDescent="0.25">
+      <c r="K18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L18" s="3">
+        <f>SUM(L9:L17)</f>
+        <v>40</v>
+      </c>
+      <c r="M18" s="3">
+        <f t="shared" ref="M18:R18" si="4">SUM(M9:M17)</f>
+        <v>28</v>
+      </c>
+      <c r="N18" s="3">
+        <f t="shared" si="4"/>
+        <v>31</v>
+      </c>
+      <c r="O18" s="3">
+        <f t="shared" si="4"/>
+        <v>27</v>
+      </c>
+      <c r="P18" s="3">
+        <f t="shared" si="4"/>
+        <v>27</v>
+      </c>
+      <c r="Q18" s="3">
+        <f t="shared" si="4"/>
+        <v>27</v>
+      </c>
+      <c r="R18" s="3">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+      <c r="S18" s="3">
+        <f>SUM(S9:S17)</f>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" spans="11:20" x14ac:dyDescent="0.25">
+      <c r="L19" s="11">
+        <f>L18/$S$18</f>
+        <v>0.18779342723004694</v>
+      </c>
+      <c r="M19" s="11">
+        <f t="shared" ref="M19:R19" si="5">M18/$S$18</f>
+        <v>0.13145539906103287</v>
+      </c>
+      <c r="N19" s="11">
+        <f t="shared" si="5"/>
+        <v>0.14553990610328638</v>
+      </c>
+      <c r="O19" s="11">
+        <f t="shared" si="5"/>
+        <v>0.12676056338028169</v>
+      </c>
+      <c r="P19" s="11">
+        <f t="shared" si="5"/>
+        <v>0.12676056338028169</v>
+      </c>
+      <c r="Q19" s="11">
+        <f t="shared" si="5"/>
+        <v>0.12676056338028169</v>
+      </c>
+      <c r="R19" s="11">
+        <f t="shared" si="5"/>
+        <v>0.15492957746478872</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE4DF7AE-4F48-4733-A00A-FE1F6AB5D7A3}">
+  <dimension ref="B1:BK82"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="52"/>
+    <col min="2" max="2" width="14.42578125" style="52" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="11.42578125" style="52"/>
+    <col min="11" max="11" width="11.42578125" style="87"/>
+    <col min="12" max="14" width="11.42578125" style="52"/>
+    <col min="15" max="15" width="14.85546875" style="52" bestFit="1" customWidth="1"/>
+    <col min="16" max="23" width="11.42578125" style="52"/>
+    <col min="24" max="24" width="11.42578125" style="87"/>
+    <col min="25" max="26" width="11.42578125" style="52"/>
+    <col min="27" max="27" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="35" width="11.42578125" style="52"/>
+    <col min="36" max="36" width="11.42578125" style="87"/>
+    <col min="37" max="38" width="11.42578125" style="52"/>
+    <col min="39" max="39" width="21.140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="40" max="47" width="11.42578125" style="52"/>
+    <col min="48" max="48" width="11.42578125" style="87"/>
+    <col min="49" max="51" width="11.42578125" style="52"/>
+    <col min="52" max="52" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="53" max="63" width="11.42578125" style="96"/>
+    <col min="64" max="16384" width="11.42578125" style="52"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="D1" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="E1" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="F1" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="H1" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="I1" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="K1" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1" s="53" t="s">
+        <v>73</v>
+      </c>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="R1" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="S1" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="U1" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="V1" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="W1" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="X1" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z1" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA1" s="60"/>
+      <c r="AB1" s="60"/>
+      <c r="AC1" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AD1" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="AE1" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="AF1" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AG1" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="AH1" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI1" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="AJ1" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AK1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL1" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AP1" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="AQ1" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="AR1" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AS1" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="AT1" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="AU1" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="AV1" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AW1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AX1" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AZ1" s="96"/>
+      <c r="BB1" s="90" t="s">
+        <v>303</v>
+      </c>
+      <c r="BC1" s="92" t="s">
+        <v>297</v>
+      </c>
+      <c r="BD1" s="94" t="s">
+        <v>298</v>
+      </c>
+      <c r="BE1" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="BF1" s="91" t="s">
+        <v>302</v>
+      </c>
+      <c r="BG1" s="93" t="s">
+        <v>15</v>
+      </c>
+      <c r="BH1" s="95" t="s">
+        <v>299</v>
+      </c>
+      <c r="BI1" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="BJ1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="BK1" s="53" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B2" s="129" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="129"/>
+      <c r="D2" s="52">
+        <f>COUNTIF(C3:C80,"GRASS")</f>
+        <v>7</v>
+      </c>
+      <c r="E2" s="52">
+        <f>COUNTIF($C$3:$C$80,"fire")</f>
+        <v>7</v>
+      </c>
+      <c r="F2" s="52">
+        <f>COUNTIF($C$3:$C$80,"water")</f>
+        <v>7</v>
+      </c>
+      <c r="G2" s="52">
+        <f>COUNTIF($C$3:$C$80,"lightning")</f>
+        <v>7</v>
+      </c>
+      <c r="H2" s="52">
+        <f>COUNTIF($C$3:$C$80,"fighting")</f>
+        <v>7</v>
+      </c>
+      <c r="I2" s="52">
+        <f>COUNTIF($C$3:$C$80,"psychic")</f>
+        <v>7</v>
+      </c>
+      <c r="J2" s="52">
+        <f>COUNTIF($C$3:$C$80,"darkness")</f>
+        <v>7</v>
+      </c>
+      <c r="K2" s="87">
+        <f>COUNTIF($C$3:$C$80,"METAL")</f>
+        <v>7</v>
+      </c>
+      <c r="L2" s="60">
+        <f>COUNTIF($C$3:$C$80,"colorless")</f>
+        <v>8</v>
+      </c>
+      <c r="M2" s="52">
+        <f>COUNTIF($C$3:$C$80,"trainers")</f>
+        <v>8</v>
+      </c>
+      <c r="N2" s="52">
+        <v>8</v>
+      </c>
+      <c r="O2" s="129" t="s">
+        <v>74</v>
+      </c>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="60">
+        <f>COUNTIF(P3:P82,"GRASS")</f>
+        <v>7</v>
+      </c>
+      <c r="R2" s="60">
+        <f>COUNTIF($P$3:$P$82,"fire")</f>
+        <v>9</v>
+      </c>
+      <c r="S2" s="60">
+        <f>COUNTIF($P$3:$P$82,"water")</f>
+        <v>9</v>
+      </c>
+      <c r="T2" s="60">
+        <f>COUNTIF($P$3:$P$82,"lightning")</f>
+        <v>8</v>
+      </c>
+      <c r="U2" s="60">
+        <f>COUNTIF($P$2:$P$65,"fighting")</f>
+        <v>8</v>
+      </c>
+      <c r="V2" s="60">
+        <f>COUNTIF($P$3:$P$82,"psychic")</f>
+        <v>7</v>
+      </c>
+      <c r="W2" s="60">
+        <f>COUNTIF($P$3:$P$82,"darkness")</f>
+        <v>9</v>
+      </c>
+      <c r="X2" s="87">
+        <f>COUNTIF($P$3:$P$82,"METAL")</f>
+        <v>7</v>
+      </c>
+      <c r="Y2" s="60">
+        <f>COUNTIF($P$3:$P$80,"colorless")</f>
+        <v>8</v>
+      </c>
+      <c r="Z2" s="60">
+        <f>COUNTIF($P$3:$P$82,"trainers")</f>
+        <v>8</v>
+      </c>
+      <c r="AA2" s="129" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB2" s="129"/>
+      <c r="AC2" s="60">
+        <f>COUNTIF(AB3:AB64,"GRASS")</f>
+        <v>9</v>
+      </c>
+      <c r="AD2" s="60">
+        <f>COUNTIF($AB$3:$AB$64,"fire")</f>
+        <v>7</v>
+      </c>
+      <c r="AE2" s="60">
+        <f>COUNTIF($AB$3:$AB$64,"water")</f>
+        <v>7</v>
+      </c>
+      <c r="AF2" s="60">
+        <f>COUNTIF($AB$3:$AB$64,"lightning")</f>
+        <v>8</v>
+      </c>
+      <c r="AG2" s="60">
+        <f>COUNTIF($AB$3:$AB$64,"fighting")</f>
+        <v>7</v>
+      </c>
+      <c r="AH2" s="60">
+        <f>COUNTIF($AB$3:$AB$64,"psychic")</f>
+        <v>7</v>
+      </c>
+      <c r="AI2" s="60">
+        <f>COUNTIF($AB$3:$AB$64,"darkness")</f>
+        <v>8</v>
+      </c>
+      <c r="AJ2" s="87">
+        <f>COUNTIF($AB$3:$AB$64,"metal")</f>
+        <v>7</v>
+      </c>
+      <c r="AK2" s="60">
+        <f>COUNTIF($AB$3:$AB$81,"colorless")</f>
+        <v>7</v>
+      </c>
+      <c r="AL2" s="60">
+        <f>COUNTIF($AB$3:$AB$81,"trainers")</f>
+        <v>10</v>
+      </c>
+      <c r="AM2" s="129" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN2" s="129"/>
+      <c r="AO2" s="60">
+        <f>COUNTIF(AN3:AN80,"GRASS")</f>
+        <v>8</v>
+      </c>
+      <c r="AP2" s="60">
+        <f>COUNTIF($AN$3:$AN$80,"fire")</f>
+        <v>9</v>
+      </c>
+      <c r="AQ2" s="60">
+        <f>COUNTIF($AN$3:$AN$80,"water")</f>
+        <v>8</v>
+      </c>
+      <c r="AR2" s="60">
+        <f>COUNTIF($AN$2:$AN$79,"lightning")</f>
+        <v>8</v>
+      </c>
+      <c r="AS2" s="60">
+        <f>COUNTIF($AN$3:$AN$80,"fighting")</f>
+        <v>6</v>
+      </c>
+      <c r="AT2" s="60">
+        <f>COUNTIF($AN$3:$AN$80,"psychic")</f>
+        <v>5</v>
+      </c>
+      <c r="AU2" s="60">
+        <f>COUNTIF($AN$3:$AN$80,"darkness")</f>
+        <v>7</v>
+      </c>
+      <c r="AV2" s="87">
+        <f>COUNTIF($AN$3:$AN$80,"metal")</f>
+        <v>8</v>
+      </c>
+      <c r="AW2" s="60">
+        <f>COUNTIF($AN$3:$AN$80,"colorless")</f>
+        <v>9</v>
+      </c>
+      <c r="AX2" s="60">
+        <f>COUNTIF($AN$3:$AN$80,"trainers")</f>
+        <v>7</v>
+      </c>
+      <c r="AZ2" s="129" t="s">
+        <v>418</v>
+      </c>
+      <c r="BA2" s="129"/>
+      <c r="BB2" s="96">
+        <f>COUNTIF(BA3:BA64,"GRASS")</f>
+        <v>7</v>
+      </c>
+      <c r="BC2" s="96">
+        <f>COUNTIF($BA$3:$BA$64,"fire")</f>
+        <v>1</v>
+      </c>
+      <c r="BD2" s="96">
+        <f>COUNTIF($BA$3:$BA$64,"water")</f>
+        <v>5</v>
+      </c>
+      <c r="BE2" s="96">
+        <f>COUNTIF($BA$3:$BA$64,"lightning")</f>
+        <v>7</v>
+      </c>
+      <c r="BF2" s="96">
+        <f>COUNTIF($BA$3:$BA$64,"fighting")</f>
+        <v>9</v>
+      </c>
+      <c r="BG2" s="96">
+        <f>COUNTIF($BA$3:$BA$64,"psychic")</f>
+        <v>7</v>
+      </c>
+      <c r="BH2" s="96">
+        <f>COUNTIF($BA$3:$BA$64,"darkness")</f>
+        <v>2</v>
+      </c>
+      <c r="BI2" s="96">
+        <f>COUNTIF($BA$3:$BA$64,"metal")</f>
+        <v>4</v>
+      </c>
+      <c r="BJ2" s="96">
+        <f>COUNTIF($BA$3:$BA$81,"colorless")</f>
+        <v>1</v>
+      </c>
+      <c r="BK2" s="96">
+        <f>COUNTIF($BA$3:$BA$81,"trainers")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B3" s="14" t="str">
+        <f>Sheet1!B3</f>
+        <v>Chikorita</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="52">
+        <f>SUM(D2:N2)</f>
+        <v>80</v>
+      </c>
+      <c r="O3" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q3" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="R3" s="60">
+        <f>SUM(Q2:AA2)</f>
+        <v>80</v>
+      </c>
+      <c r="S3" s="60"/>
+      <c r="T3" s="60"/>
+      <c r="U3" s="60"/>
+      <c r="V3" s="60"/>
+      <c r="W3" s="60"/>
+      <c r="Y3" s="60"/>
+      <c r="Z3" s="60"/>
+      <c r="AA3" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB3" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC3" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD3" s="60">
+        <f>SUM(AC2:AM2)+1</f>
+        <v>78</v>
+      </c>
+      <c r="AE3" s="60"/>
+      <c r="AF3" s="60"/>
+      <c r="AG3" s="60"/>
+      <c r="AH3" s="60"/>
+      <c r="AI3" s="60"/>
+      <c r="AK3" s="60"/>
+      <c r="AL3" s="60"/>
+      <c r="AM3" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN3" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AO3" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP3" s="60">
+        <f>SUM(AO2:AX2)</f>
+        <v>75</v>
+      </c>
+      <c r="AQ3" s="60"/>
+      <c r="AR3" s="60"/>
+      <c r="AS3" s="60"/>
+      <c r="AT3" s="60"/>
+      <c r="AU3" s="60"/>
+      <c r="AW3" s="60"/>
+      <c r="AX3" s="60"/>
+      <c r="AZ3" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="BA3" s="90" t="s">
+        <v>303</v>
+      </c>
+      <c r="BB3" s="96" t="s">
+        <v>9</v>
+      </c>
+      <c r="BC3" s="96">
+        <f>SUM(BB2:BK2)</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B4" s="14" t="str">
+        <f>Sheet1!B4</f>
+        <v>Bayleef</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="P4" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q4" s="60"/>
+      <c r="R4" s="60"/>
+      <c r="S4" s="60"/>
+      <c r="T4" s="60"/>
+      <c r="U4" s="60"/>
+      <c r="V4" s="60"/>
+      <c r="W4" s="60"/>
+      <c r="Y4" s="60"/>
+      <c r="Z4" s="60"/>
+      <c r="AA4" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="AB4" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC4" s="60"/>
+      <c r="AD4" s="60"/>
+      <c r="AE4" s="60"/>
+      <c r="AF4" s="60"/>
+      <c r="AG4" s="60"/>
+      <c r="AH4" s="60"/>
+      <c r="AI4" s="60"/>
+      <c r="AK4" s="60"/>
+      <c r="AL4" s="60"/>
+      <c r="AM4" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="AN4" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AO4" s="60"/>
+      <c r="AP4" s="60"/>
+      <c r="AQ4" s="60"/>
+      <c r="AR4" s="61"/>
+      <c r="AS4" s="60"/>
+      <c r="AT4" s="60"/>
+      <c r="AU4" s="60"/>
+      <c r="AW4" s="60"/>
+      <c r="AX4" s="60"/>
+      <c r="AZ4" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="BA4" s="90" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="5" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="str">
+        <f>Sheet1!B5</f>
+        <v>Meganium</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="P5" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q5" s="60"/>
+      <c r="R5" s="60"/>
+      <c r="S5" s="60"/>
+      <c r="T5" s="60"/>
+      <c r="U5" s="60"/>
+      <c r="V5" s="60"/>
+      <c r="W5" s="60"/>
+      <c r="Y5" s="60"/>
+      <c r="Z5" s="60"/>
+      <c r="AA5" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB5" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC5" s="60"/>
+      <c r="AD5" s="60"/>
+      <c r="AE5" s="60"/>
+      <c r="AF5" s="60"/>
+      <c r="AG5" s="60"/>
+      <c r="AH5" s="60"/>
+      <c r="AI5" s="60"/>
+      <c r="AK5" s="60"/>
+      <c r="AL5" s="60"/>
+      <c r="AM5" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="AN5" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AO5" s="60"/>
+      <c r="AP5" s="37"/>
+      <c r="AQ5" s="60"/>
+      <c r="AR5" s="37"/>
+      <c r="AS5" s="60"/>
+      <c r="AT5" s="60"/>
+      <c r="AU5" s="60"/>
+      <c r="AW5" s="60"/>
+      <c r="AX5" s="60"/>
+      <c r="AZ5" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="BA5" s="90" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="6" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B6" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q6" s="60"/>
+      <c r="R6" s="60"/>
+      <c r="S6" s="60"/>
+      <c r="T6" s="60"/>
+      <c r="U6" s="60"/>
+      <c r="V6" s="60"/>
+      <c r="W6" s="60"/>
+      <c r="Y6" s="60"/>
+      <c r="Z6" s="60"/>
+      <c r="AA6" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB6" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC6" s="60"/>
+      <c r="AD6" s="60"/>
+      <c r="AE6" s="60"/>
+      <c r="AF6" s="60"/>
+      <c r="AG6" s="60"/>
+      <c r="AH6" s="60"/>
+      <c r="AI6" s="60"/>
+      <c r="AK6" s="60"/>
+      <c r="AL6" s="60"/>
+      <c r="AM6" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN6" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AO6" s="60"/>
+      <c r="AP6" s="60"/>
+      <c r="AQ6" s="60"/>
+      <c r="AR6" s="60"/>
+      <c r="AS6" s="60"/>
+      <c r="AT6" s="60"/>
+      <c r="AU6" s="60"/>
+      <c r="AW6" s="60"/>
+      <c r="AX6" s="60"/>
+      <c r="AZ6" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="BA6" s="97" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="7" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B7" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="P7" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q7" s="60"/>
+      <c r="R7" s="60"/>
+      <c r="S7" s="60"/>
+      <c r="T7" s="60"/>
+      <c r="U7" s="60"/>
+      <c r="V7" s="60"/>
+      <c r="W7" s="60"/>
+      <c r="Y7" s="60"/>
+      <c r="Z7" s="60"/>
+      <c r="AA7" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB7" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC7" s="60"/>
+      <c r="AD7" s="60"/>
+      <c r="AE7" s="60"/>
+      <c r="AF7" s="60"/>
+      <c r="AG7" s="60"/>
+      <c r="AH7" s="60"/>
+      <c r="AI7" s="60"/>
+      <c r="AK7" s="60"/>
+      <c r="AL7" s="60"/>
+      <c r="AM7" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="AN7" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AO7" s="60"/>
+      <c r="AP7" s="60"/>
+      <c r="AQ7" s="60"/>
+      <c r="AR7" s="60"/>
+      <c r="AS7" s="60"/>
+      <c r="AT7" s="60"/>
+      <c r="AU7" s="60"/>
+      <c r="AW7" s="60"/>
+      <c r="AX7" s="60"/>
+      <c r="AZ7" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="BA7" s="97" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="8" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B8" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="O8" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="P8" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q8" s="60"/>
+      <c r="R8" s="60"/>
+      <c r="S8" s="60"/>
+      <c r="T8" s="60"/>
+      <c r="U8" s="60"/>
+      <c r="V8" s="60"/>
+      <c r="W8" s="60"/>
+      <c r="Y8" s="60"/>
+      <c r="Z8" s="60"/>
+      <c r="AA8" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB8" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC8" s="60"/>
+      <c r="AD8" s="60"/>
+      <c r="AE8" s="60"/>
+      <c r="AF8" s="60"/>
+      <c r="AG8" s="60"/>
+      <c r="AH8" s="60"/>
+      <c r="AI8" s="60"/>
+      <c r="AK8" s="60"/>
+      <c r="AL8" s="60"/>
+      <c r="AM8" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN8" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AO8" s="60"/>
+      <c r="AP8" s="60"/>
+      <c r="AQ8" s="60"/>
+      <c r="AR8" s="60"/>
+      <c r="AS8" s="60"/>
+      <c r="AT8" s="60"/>
+      <c r="AU8" s="60"/>
+      <c r="AW8" s="60"/>
+      <c r="AX8" s="60"/>
+      <c r="AZ8" s="14" t="s">
+        <v>427</v>
+      </c>
+      <c r="BA8" s="99" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="9" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B9" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="P9" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q9" s="60"/>
+      <c r="R9" s="60"/>
+      <c r="S9" s="60"/>
+      <c r="T9" s="60"/>
+      <c r="U9" s="60"/>
+      <c r="V9" s="60"/>
+      <c r="W9" s="60"/>
+      <c r="Y9" s="60"/>
+      <c r="Z9" s="60"/>
+      <c r="AA9" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB9" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC9" s="60"/>
+      <c r="AD9" s="60"/>
+      <c r="AE9" s="60"/>
+      <c r="AF9" s="60"/>
+      <c r="AG9" s="60"/>
+      <c r="AH9" s="60"/>
+      <c r="AI9" s="60"/>
+      <c r="AK9" s="60"/>
+      <c r="AL9" s="60"/>
+      <c r="AM9" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN9" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AO9" s="60"/>
+      <c r="AP9" s="60"/>
+      <c r="AQ9" s="60"/>
+      <c r="AR9" s="60"/>
+      <c r="AS9" s="60"/>
+      <c r="AT9" s="60"/>
+      <c r="AU9" s="60"/>
+      <c r="AW9" s="60"/>
+      <c r="AX9" s="60"/>
+      <c r="AZ9" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="BA9" s="99" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="10" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B10" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>297</v>
+      </c>
+      <c r="O10" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="P10" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q10" s="60"/>
+      <c r="R10" s="60"/>
+      <c r="S10" s="60"/>
+      <c r="T10" s="60"/>
+      <c r="U10" s="60"/>
+      <c r="V10" s="60"/>
+      <c r="W10" s="60"/>
+      <c r="Y10" s="60"/>
+      <c r="Z10" s="60"/>
+      <c r="AA10" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="AB10" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC10" s="60"/>
+      <c r="AD10" s="60"/>
+      <c r="AE10" s="60"/>
+      <c r="AF10" s="60"/>
+      <c r="AG10" s="60"/>
+      <c r="AH10" s="60"/>
+      <c r="AI10" s="60"/>
+      <c r="AK10" s="60"/>
+      <c r="AL10" s="60"/>
+      <c r="AM10" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN10" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AO10" s="60"/>
+      <c r="AP10" s="60"/>
+      <c r="AQ10" s="60"/>
+      <c r="AR10" s="60"/>
+      <c r="AS10" s="60"/>
+      <c r="AT10" s="60"/>
+      <c r="AU10" s="60"/>
+      <c r="AW10" s="60"/>
+      <c r="AX10" s="60"/>
+      <c r="AZ10" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="BA10" s="56" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="11" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B11" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="47" t="s">
+        <v>297</v>
+      </c>
+      <c r="O11" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="P11" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q11" s="60"/>
+      <c r="R11" s="60"/>
+      <c r="S11" s="60"/>
+      <c r="T11" s="60"/>
+      <c r="U11" s="60"/>
+      <c r="V11" s="60"/>
+      <c r="W11" s="60"/>
+      <c r="Y11" s="60"/>
+      <c r="Z11" s="60"/>
+      <c r="AA11" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB11" s="54" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC11" s="60"/>
+      <c r="AD11" s="60"/>
+      <c r="AE11" s="60"/>
+      <c r="AF11" s="60"/>
+      <c r="AG11" s="60"/>
+      <c r="AH11" s="60"/>
+      <c r="AI11" s="60"/>
+      <c r="AK11" s="60"/>
+      <c r="AL11" s="60"/>
+      <c r="AM11" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN11" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="AO11" s="60"/>
+      <c r="AP11" s="60"/>
+      <c r="AQ11" s="60"/>
+      <c r="AR11" s="60"/>
+      <c r="AS11" s="60"/>
+      <c r="AT11" s="60"/>
+      <c r="AU11" s="60"/>
+      <c r="AW11" s="60"/>
+      <c r="AX11" s="60"/>
+      <c r="AZ11" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="BA11" s="94" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="12" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B12" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>297</v>
+      </c>
+      <c r="O12" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="P12" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q12" s="60"/>
+      <c r="R12" s="60"/>
+      <c r="S12" s="60"/>
+      <c r="T12" s="60"/>
+      <c r="U12" s="60"/>
+      <c r="V12" s="60"/>
+      <c r="W12" s="60"/>
+      <c r="Y12" s="60"/>
+      <c r="Z12" s="60"/>
+      <c r="AA12" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB12" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="AC12" s="60"/>
+      <c r="AD12" s="60"/>
+      <c r="AE12" s="60"/>
+      <c r="AF12" s="60"/>
+      <c r="AG12" s="60"/>
+      <c r="AH12" s="60"/>
+      <c r="AI12" s="60"/>
+      <c r="AK12" s="60"/>
+      <c r="AL12" s="60"/>
+      <c r="AM12" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN12" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="AO12" s="60"/>
+      <c r="AP12" s="60"/>
+      <c r="AQ12" s="60"/>
+      <c r="AR12" s="60"/>
+      <c r="AS12" s="60"/>
+      <c r="AT12" s="60"/>
+      <c r="AU12" s="60"/>
+      <c r="AV12"/>
+      <c r="AW12" s="60"/>
+      <c r="AX12" s="60"/>
+      <c r="AZ12" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="BA12" s="94" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="13" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B13" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="47" t="s">
+        <v>297</v>
+      </c>
+      <c r="O13" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="P13" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q13" s="60"/>
+      <c r="R13" s="60"/>
+      <c r="S13" s="60"/>
+      <c r="T13" s="60"/>
+      <c r="U13" s="60"/>
+      <c r="V13" s="60"/>
+      <c r="W13" s="60"/>
+      <c r="Y13" s="60"/>
+      <c r="Z13" s="60"/>
+      <c r="AA13" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB13" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="AC13" s="60"/>
+      <c r="AD13" s="60"/>
+      <c r="AE13" s="60"/>
+      <c r="AF13" s="60"/>
+      <c r="AG13" s="60"/>
+      <c r="AH13" s="60"/>
+      <c r="AI13" s="60"/>
+      <c r="AK13" s="60"/>
+      <c r="AL13" s="60"/>
+      <c r="AM13" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="AN13" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="AO13" s="60"/>
+      <c r="AP13" s="60"/>
+      <c r="AQ13" s="60"/>
+      <c r="AX13" s="60"/>
+      <c r="AZ13" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="BA13" s="94" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="14" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B14" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>297</v>
+      </c>
+      <c r="O14" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="P14" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q14" s="60"/>
+      <c r="R14" s="60"/>
+      <c r="S14" s="60"/>
+      <c r="T14" s="60"/>
+      <c r="U14" s="60"/>
+      <c r="V14" s="60"/>
+      <c r="W14" s="60"/>
+      <c r="Y14" s="60"/>
+      <c r="Z14" s="60"/>
+      <c r="AA14" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB14" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="AC14" s="60"/>
+      <c r="AD14" s="60"/>
+      <c r="AE14" s="60"/>
+      <c r="AF14" s="60"/>
+      <c r="AG14" s="60"/>
+      <c r="AH14" s="60"/>
+      <c r="AI14" s="60"/>
+      <c r="AK14" s="60"/>
+      <c r="AL14" s="60"/>
+      <c r="AM14" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="AN14" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="AO14" s="60"/>
+      <c r="AP14" s="60"/>
+      <c r="AQ14" s="60"/>
+      <c r="AV14"/>
+      <c r="AW14" s="60"/>
+      <c r="AX14" s="60"/>
+      <c r="AZ14" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="BA14" s="58" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="15" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B15" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>297</v>
+      </c>
+      <c r="O15" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="P15" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q15" s="60"/>
+      <c r="R15" s="60"/>
+      <c r="S15" s="60"/>
+      <c r="T15" s="60"/>
+      <c r="U15" s="60"/>
+      <c r="V15" s="60"/>
+      <c r="W15" s="60"/>
+      <c r="Y15" s="60"/>
+      <c r="Z15" s="60"/>
+      <c r="AA15" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB15" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="AC15" s="60"/>
+      <c r="AD15" s="60"/>
+      <c r="AE15" s="60"/>
+      <c r="AF15" s="60"/>
+      <c r="AG15" s="60"/>
+      <c r="AH15" s="60"/>
+      <c r="AI15" s="60"/>
+      <c r="AK15" s="60"/>
+      <c r="AL15" s="60"/>
+      <c r="AM15" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="AN15" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="AO15" s="60"/>
+      <c r="AP15" s="60"/>
+      <c r="AQ15" s="60"/>
+      <c r="AV15"/>
+      <c r="AW15" s="60"/>
+      <c r="AX15" s="60"/>
+      <c r="AZ15" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="BA15" s="109" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="16" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B16" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>297</v>
+      </c>
+      <c r="O16" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="P16" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q16" s="60"/>
+      <c r="R16" s="60"/>
+      <c r="S16" s="60"/>
+      <c r="T16" s="60"/>
+      <c r="U16" s="60"/>
+      <c r="V16" s="60"/>
+      <c r="W16" s="60"/>
+      <c r="Y16" s="60"/>
+      <c r="Z16" s="60"/>
+      <c r="AA16" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="AB16" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="AC16" s="60"/>
+      <c r="AD16" s="60"/>
+      <c r="AE16" s="60"/>
+      <c r="AF16" s="60"/>
+      <c r="AG16" s="60"/>
+      <c r="AH16" s="60"/>
+      <c r="AI16" s="60"/>
+      <c r="AK16" s="60"/>
+      <c r="AL16" s="60"/>
+      <c r="AM16" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="AN16" s="85" t="s">
+        <v>297</v>
+      </c>
+      <c r="AO16" s="60"/>
+      <c r="AP16" s="60"/>
+      <c r="AQ16" s="60"/>
+      <c r="AT16" s="60"/>
+      <c r="AU16" s="60"/>
+      <c r="AX16" s="60"/>
+      <c r="AZ16" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="BA16" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="17" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B17" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>298</v>
+      </c>
+      <c r="O17" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="P17" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q17" s="60"/>
+      <c r="R17" s="60"/>
+      <c r="S17" s="60"/>
+      <c r="T17" s="60"/>
+      <c r="U17" s="60"/>
+      <c r="V17" s="60"/>
+      <c r="W17" s="60"/>
+      <c r="Y17" s="60"/>
+      <c r="Z17" s="60"/>
+      <c r="AA17" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="AB17" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="AC17" s="60"/>
+      <c r="AD17" s="60"/>
+      <c r="AE17" s="60"/>
+      <c r="AF17" s="60"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="60"/>
+      <c r="AK17" s="60"/>
+      <c r="AL17" s="60"/>
+      <c r="AM17" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN17" s="85" t="s">
+        <v>297</v>
+      </c>
+      <c r="AO17" s="60"/>
+      <c r="AP17" s="60"/>
+      <c r="AQ17" s="60"/>
+      <c r="AX17" s="60"/>
+      <c r="AZ17" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="BA17" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B18" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="48" t="s">
+        <v>298</v>
+      </c>
+      <c r="O18" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="P18" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q18" s="60"/>
+      <c r="R18" s="60"/>
+      <c r="S18" s="60"/>
+      <c r="T18" s="60"/>
+      <c r="U18" s="60"/>
+      <c r="V18" s="60"/>
+      <c r="W18" s="60"/>
+      <c r="Y18" s="60"/>
+      <c r="Z18" s="60"/>
+      <c r="AA18" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB18" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="AC18" s="60"/>
+      <c r="AD18" s="60"/>
+      <c r="AE18" s="60"/>
+      <c r="AF18" s="60"/>
+      <c r="AG18" s="60"/>
+      <c r="AH18" s="60"/>
+      <c r="AI18" s="60"/>
+      <c r="AK18" s="60"/>
+      <c r="AL18" s="60"/>
+      <c r="AM18" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="AN18" s="85" t="s">
+        <v>297</v>
+      </c>
+      <c r="AO18" s="60"/>
+      <c r="AP18" s="60"/>
+      <c r="AQ18" s="60"/>
+      <c r="AX18" s="60"/>
+      <c r="AZ18" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="BA18" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B19" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="48" t="s">
+        <v>298</v>
+      </c>
+      <c r="O19" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="P19" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q19" s="60"/>
+      <c r="R19" s="60"/>
+      <c r="S19" s="60"/>
+      <c r="T19" s="60"/>
+      <c r="U19" s="60"/>
+      <c r="V19" s="60"/>
+      <c r="W19" s="60"/>
+      <c r="Y19" s="60"/>
+      <c r="Z19" s="60"/>
+      <c r="AA19" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB19" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="AC19" s="60"/>
+      <c r="AD19" s="60"/>
+      <c r="AE19" s="60"/>
+      <c r="AF19" s="60"/>
+      <c r="AG19" s="60"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="60"/>
+      <c r="AK19" s="60"/>
+      <c r="AL19" s="60"/>
+      <c r="AM19" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN19" s="56" t="s">
+        <v>297</v>
+      </c>
+      <c r="AO19" s="60"/>
+      <c r="AP19" s="60"/>
+      <c r="AQ19" s="60"/>
+      <c r="AR19" s="60"/>
+      <c r="AS19" s="60"/>
+      <c r="AV19"/>
+      <c r="AW19" s="60"/>
+      <c r="AX19" s="60"/>
+      <c r="AZ19" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="BA19" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B20" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>298</v>
+      </c>
+      <c r="O20" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="P20" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q20" s="60"/>
+      <c r="R20" s="60"/>
+      <c r="S20" s="60"/>
+      <c r="T20" s="60"/>
+      <c r="U20" s="60"/>
+      <c r="V20" s="60"/>
+      <c r="W20" s="60"/>
+      <c r="Y20" s="60"/>
+      <c r="Z20" s="60"/>
+      <c r="AA20" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="AB20" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="AC20" s="60"/>
+      <c r="AD20" s="60"/>
+      <c r="AE20" s="60"/>
+      <c r="AK20" s="60"/>
+      <c r="AL20" s="60"/>
+      <c r="AM20" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="AN20" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="AO20" s="60"/>
+      <c r="AP20" s="60"/>
+      <c r="AQ20" s="60"/>
+      <c r="AR20" s="60"/>
+      <c r="AS20" s="60"/>
+      <c r="AT20" s="60"/>
+      <c r="AU20" s="60"/>
+      <c r="AV20"/>
+      <c r="AW20" s="60"/>
+      <c r="AX20" s="60"/>
+      <c r="AZ20" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="BA20" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B21" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" s="48" t="s">
+        <v>298</v>
+      </c>
+      <c r="O21" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="P21" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q21" s="60"/>
+      <c r="V21" s="60"/>
+      <c r="W21" s="60"/>
+      <c r="Y21" s="60"/>
+      <c r="Z21" s="60"/>
+      <c r="AA21" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB21" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="AC21" s="60"/>
+      <c r="AD21" s="60"/>
+      <c r="AE21" s="60"/>
+      <c r="AK21" s="60"/>
+      <c r="AL21" s="60"/>
+      <c r="AM21" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="AN21" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="AO21" s="60"/>
+      <c r="AP21" s="60"/>
+      <c r="AQ21" s="60"/>
+      <c r="AR21" s="60"/>
+      <c r="AS21" s="60"/>
+      <c r="AV21"/>
+      <c r="AW21" s="60"/>
+      <c r="AX21" s="60"/>
+      <c r="AZ21" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="BA21" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B22" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>298</v>
+      </c>
+      <c r="O22" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="P22" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q22" s="60"/>
+      <c r="V22" s="60"/>
+      <c r="W22" s="60"/>
+      <c r="Y22" s="60"/>
+      <c r="Z22" s="60"/>
+      <c r="AA22" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB22" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="AC22" s="60"/>
+      <c r="AD22" s="60"/>
+      <c r="AE22" s="60"/>
+      <c r="AK22" s="60"/>
+      <c r="AL22" s="60"/>
+      <c r="AM22" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="AN22" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="AO22" s="60"/>
+      <c r="AP22" s="60"/>
+      <c r="AQ22" s="60"/>
+      <c r="AR22" s="60"/>
+      <c r="AS22" s="60"/>
+      <c r="AT22" s="60"/>
+      <c r="AU22" s="60"/>
+      <c r="AV22"/>
+      <c r="AW22" s="60"/>
+      <c r="AX22" s="60"/>
+      <c r="AZ22" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="BA22" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="23" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B23" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" s="48" t="s">
+        <v>298</v>
+      </c>
+      <c r="O23" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="P23" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q23" s="60"/>
+      <c r="V23" s="60"/>
+      <c r="W23" s="60"/>
+      <c r="Y23" s="60"/>
+      <c r="Z23" s="60"/>
+      <c r="AA23" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB23" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="AC23" s="60"/>
+      <c r="AD23" s="60"/>
+      <c r="AE23" s="60"/>
+      <c r="AK23" s="60"/>
+      <c r="AL23" s="60"/>
+      <c r="AM23" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="AN23" s="94" t="s">
+        <v>298</v>
+      </c>
+      <c r="AO23" s="60"/>
+      <c r="AP23" s="60"/>
+      <c r="AQ23" s="60"/>
+      <c r="AR23" s="60"/>
+      <c r="AS23" s="60"/>
+      <c r="AT23" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="AU23" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="AV23"/>
+      <c r="AW23" s="60"/>
+      <c r="AX23" s="60"/>
+      <c r="AZ23" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="BA23" s="91" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="24" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B24" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="O24" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="P24" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q24" s="60"/>
+      <c r="V24" s="60"/>
+      <c r="W24" s="60"/>
+      <c r="Y24" s="60"/>
+      <c r="Z24" s="60"/>
+      <c r="AC24" s="60"/>
+      <c r="AD24" s="60"/>
+      <c r="AE24" s="60"/>
+      <c r="AK24" s="60"/>
+      <c r="AL24" s="60"/>
+      <c r="AM24" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="AN24" s="94" t="s">
+        <v>298</v>
+      </c>
+      <c r="AO24" s="60"/>
+      <c r="AP24" s="60"/>
+      <c r="AQ24" s="60"/>
+      <c r="AR24" s="60"/>
+      <c r="AS24" s="60"/>
+      <c r="AT24" s="60"/>
+      <c r="AU24" s="60"/>
+      <c r="AW24" s="60"/>
+      <c r="AX24" s="60"/>
+      <c r="AZ24" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="BA24" s="91" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="25" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B25" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="O25" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="P25" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q25" s="60"/>
+      <c r="V25" s="60"/>
+      <c r="W25" s="60"/>
+      <c r="Y25" s="60"/>
+      <c r="Z25" s="60"/>
+      <c r="AC25" s="60"/>
+      <c r="AD25" s="60"/>
+      <c r="AE25" s="60"/>
+      <c r="AK25" s="60"/>
+      <c r="AL25" s="60"/>
+      <c r="AM25" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="AN25" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="AO25" s="60"/>
+      <c r="AP25" s="60"/>
+      <c r="AQ25" s="60"/>
+      <c r="AR25" s="60"/>
+      <c r="AS25" s="60"/>
+      <c r="AT25" s="60"/>
+      <c r="AU25" s="60"/>
+      <c r="AW25" s="60"/>
+      <c r="AX25" s="60"/>
+      <c r="AZ25" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="BA25" s="55" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="26" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B26" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="O26" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="P26" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q26" s="60"/>
+      <c r="V26" s="60"/>
+      <c r="W26" s="60"/>
+      <c r="Y26" s="60"/>
+      <c r="Z26" s="60"/>
+      <c r="AA26" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="AB26" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="AC26" s="60"/>
+      <c r="AD26" s="60"/>
+      <c r="AE26" s="60"/>
+      <c r="AK26" s="60"/>
+      <c r="AL26" s="60"/>
+      <c r="AM26" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN26" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="AO26" s="60"/>
+      <c r="AP26" s="60"/>
+      <c r="AQ26" s="60"/>
+      <c r="AR26" s="60"/>
+      <c r="AS26" s="60"/>
+      <c r="AT26" s="60"/>
+      <c r="AU26" s="60"/>
+      <c r="AW26" s="60"/>
+      <c r="AX26" s="60"/>
+      <c r="AZ26" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="BA26" s="55" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="27" spans="2:53" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="O27" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="P27" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q27" s="60"/>
+      <c r="V27" s="60"/>
+      <c r="W27" s="60"/>
+      <c r="Y27" s="60"/>
+      <c r="Z27" s="60"/>
+      <c r="AA27" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="AB27" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="AC27" s="60"/>
+      <c r="AD27" s="60"/>
+      <c r="AE27" s="60"/>
+      <c r="AK27" s="60"/>
+      <c r="AL27" s="60"/>
+      <c r="AM27" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="AN27" s="48" t="s">
+        <v>298</v>
+      </c>
+      <c r="AO27" s="60"/>
+      <c r="AP27" s="60"/>
+      <c r="AQ27" s="60"/>
+      <c r="AR27" s="60"/>
+      <c r="AS27" s="60"/>
+      <c r="AT27" s="60"/>
+      <c r="AU27" s="60"/>
+      <c r="AW27" s="60"/>
+      <c r="AX27" s="60"/>
+      <c r="AZ27" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="BA27" s="55" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="28" spans="2:53" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="O28" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="P28" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q28" s="60"/>
+      <c r="V28" s="60"/>
+      <c r="W28" s="60"/>
+      <c r="Y28" s="60"/>
+      <c r="Z28" s="60"/>
+      <c r="AA28" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB28" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AC28" s="60"/>
+      <c r="AD28" s="60"/>
+      <c r="AE28" s="60"/>
+      <c r="AK28" s="60"/>
+      <c r="AL28" s="60"/>
+      <c r="AM28" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="AN28" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AO28" s="60"/>
+      <c r="AP28" s="60"/>
+      <c r="AQ28" s="60"/>
+      <c r="AR28" s="60"/>
+      <c r="AS28" s="60"/>
+      <c r="AT28" s="60"/>
+      <c r="AU28" s="60"/>
+      <c r="AW28" s="60"/>
+      <c r="AX28" s="60"/>
+      <c r="AZ28" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="BA28" s="55" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="29" spans="2:53" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="O29" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="P29" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q29" s="60"/>
+      <c r="V29" s="60"/>
+      <c r="W29" s="60"/>
+      <c r="Y29" s="60"/>
+      <c r="Z29" s="60"/>
+      <c r="AA29" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="AB29" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AC29" s="60"/>
+      <c r="AD29" s="60"/>
+      <c r="AE29" s="60"/>
+      <c r="AK29" s="60"/>
+      <c r="AL29" s="60"/>
+      <c r="AM29" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="AN29" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AO29" s="60"/>
+      <c r="AP29" s="60"/>
+      <c r="AQ29" s="60"/>
+      <c r="AR29" s="60"/>
+      <c r="AS29" s="60"/>
+      <c r="AT29" s="60"/>
+      <c r="AU29" s="60"/>
+      <c r="AW29" s="60"/>
+      <c r="AX29" s="60"/>
+      <c r="AZ29" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="BA29" s="98" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="30" spans="2:53" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="O30" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q30" s="60"/>
+      <c r="V30" s="60"/>
+      <c r="W30" s="60"/>
+      <c r="Y30" s="60"/>
+      <c r="Z30" s="60"/>
+      <c r="AA30" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB30" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AC30" s="60"/>
+      <c r="AD30" s="60"/>
+      <c r="AE30" s="60"/>
+      <c r="AK30" s="60"/>
+      <c r="AL30" s="60"/>
+      <c r="AM30" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="AN30" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AO30" s="60"/>
+      <c r="AP30" s="60"/>
+      <c r="AQ30" s="60"/>
+      <c r="AR30" s="60"/>
+      <c r="AS30" s="60"/>
+      <c r="AT30" s="60"/>
+      <c r="AU30" s="60"/>
+      <c r="AW30" s="60"/>
+      <c r="AX30" s="60"/>
+      <c r="AZ30" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="BA30" s="98" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="31" spans="2:53" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C31" s="49" t="s">
+        <v>302</v>
+      </c>
+      <c r="O31" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="P31" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q31" s="60"/>
+      <c r="V31" s="60"/>
+      <c r="W31" s="60"/>
+      <c r="Y31" s="60"/>
+      <c r="Z31" s="60"/>
+      <c r="AA31" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="AB31" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AC31" s="60"/>
+      <c r="AD31" s="60"/>
+      <c r="AE31" s="60"/>
+      <c r="AF31" s="60"/>
+      <c r="AG31" s="60"/>
+      <c r="AH31" s="60"/>
+      <c r="AI31" s="60"/>
+      <c r="AK31" s="60"/>
+      <c r="AL31" s="60"/>
+      <c r="AM31" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="AN31" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AO31" s="60"/>
+      <c r="AP31" s="60"/>
+      <c r="AQ31" s="60"/>
+      <c r="AR31" s="60"/>
+      <c r="AS31" s="60"/>
+      <c r="AT31" s="60"/>
+      <c r="AU31" s="60"/>
+      <c r="AW31" s="60"/>
+      <c r="AX31" s="60"/>
+      <c r="AZ31" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="BA31" s="107" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="32" spans="2:53" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C32" s="49" t="s">
+        <v>302</v>
+      </c>
+      <c r="O32" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="P32" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q32" s="60"/>
+      <c r="R32" s="60"/>
+      <c r="S32" s="60"/>
+      <c r="T32" s="60"/>
+      <c r="U32" s="60"/>
+      <c r="V32" s="60"/>
+      <c r="W32" s="60"/>
+      <c r="Y32" s="60"/>
+      <c r="Z32" s="60"/>
+      <c r="AA32" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB32" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AC32" s="60"/>
+      <c r="AD32" s="60"/>
+      <c r="AE32" s="60"/>
+      <c r="AF32" s="60"/>
+      <c r="AG32" s="60"/>
+      <c r="AH32" s="60"/>
+      <c r="AI32" s="60"/>
+      <c r="AK32" s="60"/>
+      <c r="AL32" s="60"/>
+      <c r="AM32" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN32" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AO32" s="60"/>
+      <c r="AP32" s="60"/>
+      <c r="AQ32" s="60"/>
+      <c r="AR32" s="60"/>
+      <c r="AS32" s="60"/>
+      <c r="AT32" s="60"/>
+      <c r="AU32" s="60"/>
+      <c r="AW32" s="60"/>
+      <c r="AX32" s="60"/>
+      <c r="AZ32" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="BA32" s="108" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="2:53" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="C33" s="49" t="s">
+        <v>302</v>
+      </c>
+      <c r="O33" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="P33" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q33" s="60"/>
+      <c r="R33" s="60"/>
+      <c r="S33" s="60"/>
+      <c r="T33" s="60"/>
+      <c r="U33" s="60"/>
+      <c r="V33" s="60"/>
+      <c r="W33" s="60"/>
+      <c r="Y33" s="60"/>
+      <c r="Z33" s="60"/>
+      <c r="AA33" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB33" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AC33" s="60"/>
+      <c r="AD33" s="60"/>
+      <c r="AE33" s="60"/>
+      <c r="AF33" s="60"/>
+      <c r="AG33" s="60"/>
+      <c r="AH33" s="60"/>
+      <c r="AI33" s="60"/>
+      <c r="AK33" s="60"/>
+      <c r="AL33" s="60"/>
+      <c r="AM33" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="AN33" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AO33" s="60"/>
+      <c r="AP33" s="60"/>
+      <c r="AQ33" s="60"/>
+      <c r="AR33" s="60"/>
+      <c r="AS33" s="60"/>
+      <c r="AT33" s="60"/>
+      <c r="AU33" s="60"/>
+      <c r="AW33" s="60"/>
+      <c r="AX33" s="60"/>
+      <c r="AZ33" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="BA33" s="108" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="2:53" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="C34" s="49" t="s">
+        <v>302</v>
+      </c>
+      <c r="O34" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="P34" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q34" s="60"/>
+      <c r="R34" s="60"/>
+      <c r="S34" s="60"/>
+      <c r="T34" s="60"/>
+      <c r="U34" s="60"/>
+      <c r="V34" s="60"/>
+      <c r="W34" s="60"/>
+      <c r="Y34" s="60"/>
+      <c r="Z34" s="60"/>
+      <c r="AA34" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB34" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AC34" s="60"/>
+      <c r="AD34" s="60"/>
+      <c r="AE34" s="60"/>
+      <c r="AF34" s="60"/>
+      <c r="AG34" s="60"/>
+      <c r="AH34" s="60"/>
+      <c r="AI34" s="60"/>
+      <c r="AK34" s="60"/>
+      <c r="AL34" s="60"/>
+      <c r="AM34" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="AN34" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AO34" s="60"/>
+      <c r="AP34" s="60"/>
+      <c r="AQ34" s="60"/>
+      <c r="AR34" s="60"/>
+      <c r="AS34" s="60"/>
+      <c r="AT34" s="60"/>
+      <c r="AU34" s="60"/>
+      <c r="AW34" s="60"/>
+      <c r="AX34" s="60"/>
+      <c r="AZ34" s="14" t="s">
+        <v>436</v>
+      </c>
+      <c r="BA34" s="108" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B35" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="C35" s="49" t="s">
+        <v>302</v>
+      </c>
+      <c r="O35" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q35" s="60"/>
+      <c r="R35" s="60"/>
+      <c r="S35" s="60"/>
+      <c r="T35" s="60"/>
+      <c r="U35" s="60"/>
+      <c r="V35" s="60"/>
+      <c r="W35" s="60"/>
+      <c r="Y35" s="60"/>
+      <c r="Z35" s="60"/>
+      <c r="AA35" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB35" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AC35" s="60"/>
+      <c r="AD35" s="60"/>
+      <c r="AE35" s="60"/>
+      <c r="AF35" s="60"/>
+      <c r="AG35" s="60"/>
+      <c r="AH35" s="60"/>
+      <c r="AI35" s="60"/>
+      <c r="AK35" s="60"/>
+      <c r="AL35" s="60"/>
+      <c r="AM35" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="AN35" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="AO35" s="60"/>
+      <c r="AP35" s="60"/>
+      <c r="AQ35" s="60"/>
+      <c r="AR35" s="60"/>
+      <c r="AS35" s="60"/>
+      <c r="AT35" s="60"/>
+      <c r="AU35" s="60"/>
+      <c r="AW35" s="60"/>
+      <c r="AX35" s="60"/>
+      <c r="AZ35" s="14" t="s">
+        <v>437</v>
+      </c>
+      <c r="BA35" s="108" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B36" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="C36" s="49" t="s">
+        <v>302</v>
+      </c>
+      <c r="O36" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="P36" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q36" s="60"/>
+      <c r="R36" s="60"/>
+      <c r="S36" s="60"/>
+      <c r="T36" s="60"/>
+      <c r="U36" s="60"/>
+      <c r="V36" s="60"/>
+      <c r="W36" s="60"/>
+      <c r="Y36" s="60"/>
+      <c r="Z36" s="60"/>
+      <c r="AA36" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB36" s="49" t="s">
+        <v>302</v>
+      </c>
+      <c r="AC36" s="60"/>
+      <c r="AD36" s="60"/>
+      <c r="AE36" s="60"/>
+      <c r="AF36" s="60"/>
+      <c r="AG36" s="60"/>
+      <c r="AH36" s="60"/>
+      <c r="AI36" s="60"/>
+      <c r="AK36" s="60"/>
+      <c r="AL36" s="60"/>
+      <c r="AM36" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="AN36" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="AO36" s="60"/>
+      <c r="AP36" s="60"/>
+      <c r="AQ36" s="60"/>
+      <c r="AR36" s="60"/>
+      <c r="AS36" s="60"/>
+      <c r="AT36" s="60"/>
+      <c r="AU36" s="60"/>
+      <c r="AW36" s="60"/>
+      <c r="AX36" s="60"/>
+      <c r="AZ36" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="BA36" s="114" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B37" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="C37" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="O37" s="88" t="s">
+        <v>189</v>
+      </c>
+      <c r="P37" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q37" s="60"/>
+      <c r="R37" s="60"/>
+      <c r="S37" s="60"/>
+      <c r="T37" s="60"/>
+      <c r="U37" s="60"/>
+      <c r="V37" s="60"/>
+      <c r="W37" s="60"/>
+      <c r="Y37" s="60"/>
+      <c r="Z37" s="60"/>
+      <c r="AA37" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB37" s="49" t="s">
+        <v>302</v>
+      </c>
+      <c r="AC37" s="60"/>
+      <c r="AD37" s="60"/>
+      <c r="AE37" s="60"/>
+      <c r="AF37" s="60"/>
+      <c r="AG37" s="60"/>
+      <c r="AH37" s="60"/>
+      <c r="AI37" s="60"/>
+      <c r="AK37" s="60"/>
+      <c r="AL37" s="60"/>
+      <c r="AM37" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="AN37" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="AO37" s="60"/>
+      <c r="AP37" s="60"/>
+      <c r="AQ37" s="60"/>
+      <c r="AR37" s="60"/>
+      <c r="AS37" s="60"/>
+      <c r="AT37" s="60"/>
+      <c r="AU37" s="60"/>
+      <c r="AW37" s="60"/>
+      <c r="AX37" s="60"/>
+      <c r="AZ37" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="BA37" s="114" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B38" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="C38" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="O38" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="P38" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q38" s="60"/>
+      <c r="R38" s="60"/>
+      <c r="S38" s="60"/>
+      <c r="T38" s="60"/>
+      <c r="U38" s="60"/>
+      <c r="V38" s="60"/>
+      <c r="W38" s="60"/>
+      <c r="Y38" s="60"/>
+      <c r="Z38" s="60"/>
+      <c r="AA38" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="AB38" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="AC38" s="60"/>
+      <c r="AD38" s="60"/>
+      <c r="AE38" s="60"/>
+      <c r="AF38" s="60"/>
+      <c r="AG38" s="60"/>
+      <c r="AH38" s="60"/>
+      <c r="AI38" s="60"/>
+      <c r="AK38" s="60"/>
+      <c r="AL38" s="60"/>
+      <c r="AM38" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN38" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="AO38" s="60"/>
+      <c r="AP38" s="60"/>
+      <c r="AQ38" s="60"/>
+      <c r="AR38" s="60"/>
+      <c r="AS38" s="60"/>
+      <c r="AT38" s="60"/>
+      <c r="AU38" s="60"/>
+      <c r="AW38" s="60"/>
+      <c r="AX38" s="60"/>
+      <c r="AZ38" s="14" t="s">
+        <v>457</v>
+      </c>
+      <c r="BA38" s="114" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B39" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="C39" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="O39" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="P39" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q39" s="60"/>
+      <c r="R39" s="60"/>
+      <c r="S39" s="60"/>
+      <c r="T39" s="60"/>
+      <c r="U39" s="60"/>
+      <c r="V39" s="60"/>
+      <c r="W39" s="60"/>
+      <c r="Y39" s="60"/>
+      <c r="Z39" s="60"/>
+      <c r="AA39" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB39" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="AC39" s="60"/>
+      <c r="AD39" s="60"/>
+      <c r="AE39" s="60"/>
+      <c r="AF39" s="60"/>
+      <c r="AG39" s="60"/>
+      <c r="AH39" s="60"/>
+      <c r="AI39" s="60"/>
+      <c r="AK39" s="60"/>
+      <c r="AL39" s="60"/>
+      <c r="AM39" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="AN39" s="91" t="s">
+        <v>302</v>
+      </c>
+      <c r="AO39" s="60"/>
+      <c r="AP39" s="60"/>
+      <c r="AQ39" s="60"/>
+      <c r="AR39" s="60"/>
+      <c r="AS39" s="60"/>
+      <c r="AT39" s="60"/>
+      <c r="AU39" s="60"/>
+      <c r="AW39" s="60"/>
+      <c r="AX39" s="60"/>
+      <c r="AZ39" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="BA39" s="115" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="40" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B40" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="C40" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="O40" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="P40" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q40" s="60"/>
+      <c r="R40" s="60"/>
+      <c r="S40" s="60"/>
+      <c r="T40" s="60"/>
+      <c r="U40" s="60"/>
+      <c r="V40" s="60"/>
+      <c r="W40" s="60"/>
+      <c r="Y40" s="60"/>
+      <c r="Z40" s="60"/>
+      <c r="AA40" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="AB40" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="AC40" s="60"/>
+      <c r="AD40" s="60"/>
+      <c r="AE40" s="60"/>
+      <c r="AF40" s="60"/>
+      <c r="AG40" s="60"/>
+      <c r="AH40" s="60"/>
+      <c r="AI40" s="60"/>
+      <c r="AK40" s="60"/>
+      <c r="AL40" s="60"/>
+      <c r="AM40" s="14" t="s">
+        <v>432</v>
+      </c>
+      <c r="AN40" s="91" t="s">
+        <v>302</v>
+      </c>
+      <c r="AO40" s="60"/>
+      <c r="AP40" s="60"/>
+      <c r="AQ40" s="60"/>
+      <c r="AR40" s="60"/>
+      <c r="AS40" s="60"/>
+      <c r="AT40" s="60"/>
+      <c r="AU40" s="60"/>
+      <c r="AW40" s="60"/>
+      <c r="AX40" s="60"/>
+      <c r="AZ40" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="BA40" s="115" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="41" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B41" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="C41" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="O41" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="P41" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q41" s="60"/>
+      <c r="R41" s="60"/>
+      <c r="S41" s="60"/>
+      <c r="T41" s="60"/>
+      <c r="U41" s="60"/>
+      <c r="V41" s="60"/>
+      <c r="W41" s="60"/>
+      <c r="Y41" s="60"/>
+      <c r="Z41" s="60"/>
+      <c r="AA41" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB41" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="AC41" s="60"/>
+      <c r="AD41" s="60"/>
+      <c r="AE41" s="60"/>
+      <c r="AF41" s="60"/>
+      <c r="AG41" s="60"/>
+      <c r="AH41" s="60"/>
+      <c r="AI41" s="60"/>
+      <c r="AK41" s="60"/>
+      <c r="AL41" s="60"/>
+      <c r="AM41" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="AN41" s="91" t="s">
+        <v>302</v>
+      </c>
+      <c r="AO41" s="60"/>
+      <c r="AP41" s="60"/>
+      <c r="AQ41" s="60"/>
+      <c r="AR41" s="60"/>
+      <c r="AS41" s="60"/>
+      <c r="AT41" s="60"/>
+      <c r="AU41" s="60"/>
+      <c r="AW41" s="60"/>
+      <c r="AX41" s="60"/>
+      <c r="AZ41" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="BA41" s="84" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="42" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B42" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="C42" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="O42" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="P42" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q42" s="60"/>
+      <c r="R42" s="60"/>
+      <c r="S42" s="60"/>
+      <c r="T42" s="60"/>
+      <c r="U42" s="60"/>
+      <c r="V42" s="60"/>
+      <c r="W42" s="60"/>
+      <c r="Y42" s="60"/>
+      <c r="Z42" s="60"/>
+      <c r="AA42" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="AB42" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="AC42" s="60"/>
+      <c r="AD42" s="60"/>
+      <c r="AE42" s="60"/>
+      <c r="AF42" s="60"/>
+      <c r="AG42" s="60"/>
+      <c r="AH42" s="60"/>
+      <c r="AI42" s="60"/>
+      <c r="AK42" s="60"/>
+      <c r="AL42" s="60"/>
+      <c r="AM42" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="AN42" s="100" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP42" s="60"/>
+      <c r="AQ42" s="60"/>
+      <c r="AR42" s="60"/>
+      <c r="AS42" s="60"/>
+      <c r="AT42" s="60"/>
+      <c r="AU42" s="60"/>
+      <c r="AW42" s="60"/>
+      <c r="AX42" s="60"/>
+      <c r="AZ42" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="BA42" s="84" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="43" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B43" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="C43" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="O43" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="P43" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q43" s="60"/>
+      <c r="R43" s="60"/>
+      <c r="S43" s="60"/>
+      <c r="T43" s="60"/>
+      <c r="U43" s="60"/>
+      <c r="V43" s="60"/>
+      <c r="W43" s="60"/>
+      <c r="Y43" s="60"/>
+      <c r="Z43" s="60"/>
+      <c r="AA43" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="AB43" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC43" s="60"/>
+      <c r="AD43" s="60"/>
+      <c r="AE43" s="60"/>
+      <c r="AF43" s="60"/>
+      <c r="AG43" s="60"/>
+      <c r="AH43" s="60"/>
+      <c r="AI43" s="60"/>
+      <c r="AK43" s="60"/>
+      <c r="AL43" s="60"/>
+      <c r="AM43" s="14" t="s">
+        <v>445</v>
+      </c>
+      <c r="AN43" s="100" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP43" s="60"/>
+      <c r="AQ43" s="60"/>
+      <c r="AR43" s="60"/>
+      <c r="AS43" s="60"/>
+      <c r="AT43" s="60"/>
+      <c r="AU43" s="60"/>
+      <c r="AW43" s="60"/>
+      <c r="AX43" s="60"/>
+      <c r="AZ43" s="14" t="s">
+        <v>447</v>
+      </c>
+      <c r="BA43" s="84" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="44" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B44" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="C44" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="O44" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="P44" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q44" s="60"/>
+      <c r="R44" s="60"/>
+      <c r="S44" s="60"/>
+      <c r="T44" s="60"/>
+      <c r="U44" s="60"/>
+      <c r="V44" s="60"/>
+      <c r="W44" s="60"/>
+      <c r="Y44" s="60"/>
+      <c r="Z44" s="60"/>
+      <c r="AA44" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="AB44" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC44" s="60"/>
+      <c r="AD44" s="60"/>
+      <c r="AE44" s="60"/>
+      <c r="AF44" s="60"/>
+      <c r="AG44" s="60"/>
+      <c r="AH44" s="60"/>
+      <c r="AI44" s="60"/>
+      <c r="AK44" s="60"/>
+      <c r="AL44" s="60"/>
+      <c r="AM44" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="AN44" s="100" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP44" s="60"/>
+      <c r="AQ44" s="60"/>
+      <c r="AR44" s="60"/>
+      <c r="AS44" s="60"/>
+      <c r="AT44" s="60"/>
+      <c r="AU44" s="60"/>
+      <c r="AW44" s="60"/>
+      <c r="AX44" s="60"/>
+      <c r="AZ44" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="BA44" s="84" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="45" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B45" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="C45" s="51" t="s">
+        <v>299</v>
+      </c>
+      <c r="O45" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="P45" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q45" s="60"/>
+      <c r="R45" s="60"/>
+      <c r="S45" s="60"/>
+      <c r="T45" s="60"/>
+      <c r="U45" s="60"/>
+      <c r="V45" s="60"/>
+      <c r="W45" s="60"/>
+      <c r="AA45" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB45" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC45" s="60"/>
+      <c r="AD45" s="60"/>
+      <c r="AE45" s="60"/>
+      <c r="AF45" s="60"/>
+      <c r="AG45" s="60"/>
+      <c r="AH45" s="60"/>
+      <c r="AI45" s="60"/>
+      <c r="AK45" s="60"/>
+      <c r="AL45" s="60"/>
+      <c r="AM45" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="AN45" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO45" s="60"/>
+      <c r="AR45" s="60"/>
+      <c r="AS45" s="60"/>
+      <c r="AT45" s="60"/>
+      <c r="AU45" s="60"/>
+      <c r="AW45" s="60"/>
+      <c r="AX45" s="60"/>
+      <c r="AZ45" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="BA45" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B46" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="C46" s="51" t="s">
+        <v>299</v>
+      </c>
+      <c r="O46" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="P46" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q46" s="60"/>
+      <c r="R46" s="60"/>
+      <c r="S46" s="60"/>
+      <c r="T46" s="60"/>
+      <c r="U46" s="60"/>
+      <c r="V46" s="60"/>
+      <c r="W46" s="60"/>
+      <c r="AA46" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="AB46" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC46" s="60"/>
+      <c r="AD46" s="60"/>
+      <c r="AE46" s="60"/>
+      <c r="AF46" s="60"/>
+      <c r="AG46" s="60"/>
+      <c r="AH46" s="60"/>
+      <c r="AI46" s="60"/>
+      <c r="AK46" s="60"/>
+      <c r="AL46" s="60"/>
+      <c r="AM46" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="AN46" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO46" s="60"/>
+      <c r="AR46" s="60"/>
+      <c r="AS46" s="60"/>
+      <c r="AT46" s="60"/>
+      <c r="AU46" s="60"/>
+      <c r="AW46" s="60"/>
+      <c r="AX46" s="60"/>
+      <c r="AZ46" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="BA46" s="53" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B47" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="C47" s="51" t="s">
+        <v>299</v>
+      </c>
+      <c r="O47" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="P47" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q47" s="60"/>
+      <c r="R47" s="60"/>
+      <c r="S47" s="60"/>
+      <c r="T47" s="60"/>
+      <c r="U47" s="60"/>
+      <c r="V47" s="60"/>
+      <c r="W47" s="60"/>
+      <c r="Y47" s="60"/>
+      <c r="Z47" s="60"/>
+      <c r="AA47" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="AB47" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC47" s="60"/>
+      <c r="AD47" s="60"/>
+      <c r="AE47" s="60"/>
+      <c r="AF47" s="60"/>
+      <c r="AG47" s="60"/>
+      <c r="AH47" s="60"/>
+      <c r="AI47" s="60"/>
+      <c r="AK47" s="60"/>
+      <c r="AL47" s="60"/>
+      <c r="AM47" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="AN47" s="86" t="s">
+        <v>299</v>
+      </c>
+      <c r="AO47" s="60"/>
+      <c r="AR47" s="60"/>
+      <c r="AS47" s="60"/>
+      <c r="AT47" s="60"/>
+      <c r="AU47" s="60"/>
+      <c r="AW47" s="60"/>
+      <c r="AX47" s="60"/>
+      <c r="BA47"/>
+    </row>
+    <row r="48" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B48" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="C48" s="51" t="s">
+        <v>299</v>
+      </c>
+      <c r="O48" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="P48" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q48" s="60"/>
+      <c r="R48" s="60"/>
+      <c r="S48" s="60"/>
+      <c r="T48" s="60"/>
+      <c r="U48" s="60"/>
+      <c r="V48" s="60"/>
+      <c r="W48" s="60"/>
+      <c r="Y48" s="60"/>
+      <c r="Z48" s="60"/>
+      <c r="AA48" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="AB48" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC48" s="60"/>
+      <c r="AD48" s="60"/>
+      <c r="AE48" s="60"/>
+      <c r="AF48" s="60"/>
+      <c r="AG48" s="60"/>
+      <c r="AH48" s="60"/>
+      <c r="AI48" s="60"/>
+      <c r="AK48" s="60"/>
+      <c r="AL48" s="60"/>
+      <c r="AM48" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="AN48" s="86" t="s">
+        <v>299</v>
+      </c>
+      <c r="AO48" s="60"/>
+      <c r="AR48" s="60"/>
+      <c r="AS48" s="60"/>
+      <c r="AT48" s="60"/>
+      <c r="AU48" s="60"/>
+      <c r="AW48" s="60"/>
+      <c r="AX48" s="60"/>
+      <c r="BA48"/>
+    </row>
+    <row r="49" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B49" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C49" s="51" t="s">
+        <v>299</v>
+      </c>
+      <c r="O49" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="P49" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q49" s="60"/>
+      <c r="R49" s="60"/>
+      <c r="S49" s="60"/>
+      <c r="T49" s="60"/>
+      <c r="U49" s="60"/>
+      <c r="V49" s="60"/>
+      <c r="W49" s="60"/>
+      <c r="Y49" s="60"/>
+      <c r="Z49" s="60"/>
+      <c r="AA49" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="AB49" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC49" s="60"/>
+      <c r="AD49" s="60"/>
+      <c r="AE49" s="60"/>
+      <c r="AF49" s="60"/>
+      <c r="AG49" s="60"/>
+      <c r="AH49" s="60"/>
+      <c r="AI49" s="60"/>
+      <c r="AK49" s="60"/>
+      <c r="AL49" s="60"/>
+      <c r="AM49" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AN49" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="AO49" s="60"/>
+      <c r="AR49" s="60"/>
+      <c r="AS49" s="60"/>
+      <c r="AT49" s="60"/>
+      <c r="AU49" s="60"/>
+      <c r="AW49" s="60"/>
+      <c r="AX49" s="60"/>
+      <c r="BA49"/>
+    </row>
+    <row r="50" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B50" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="C50" s="51" t="s">
+        <v>299</v>
+      </c>
+      <c r="O50" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="P50" s="57" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q50" s="60"/>
+      <c r="R50" s="60"/>
+      <c r="S50" s="60"/>
+      <c r="T50" s="60"/>
+      <c r="U50" s="60"/>
+      <c r="V50" s="60"/>
+      <c r="W50" s="60"/>
+      <c r="Y50" s="60"/>
+      <c r="Z50" s="60"/>
+      <c r="AA50" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="AB50" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="AC50" s="60"/>
+      <c r="AD50" s="60"/>
+      <c r="AE50" s="60"/>
+      <c r="AF50" s="60"/>
+      <c r="AG50" s="60"/>
+      <c r="AH50" s="60"/>
+      <c r="AI50" s="60"/>
+      <c r="AK50" s="60"/>
+      <c r="AL50" s="60"/>
+      <c r="AM50" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="AN50" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="AO50" s="60"/>
+      <c r="AP50" s="60"/>
+      <c r="AQ50" s="60"/>
+      <c r="AR50" s="60"/>
+      <c r="AS50" s="60"/>
+      <c r="AT50" s="60"/>
+      <c r="AU50" s="60"/>
+      <c r="AW50" s="60"/>
+      <c r="AX50" s="60"/>
+      <c r="BA50"/>
+    </row>
+    <row r="51" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B51" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="C51" s="51" t="s">
+        <v>299</v>
+      </c>
+      <c r="O51" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="P51" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q51" s="60"/>
+      <c r="R51" s="60"/>
+      <c r="S51" s="60"/>
+      <c r="T51" s="60"/>
+      <c r="U51" s="60"/>
+      <c r="V51" s="60"/>
+      <c r="W51" s="60"/>
+      <c r="Y51" s="60"/>
+      <c r="Z51" s="60"/>
+      <c r="AA51" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="AB51" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="AC51" s="60"/>
+      <c r="AD51" s="60"/>
+      <c r="AE51" s="60"/>
+      <c r="AF51" s="60"/>
+      <c r="AG51" s="60"/>
+      <c r="AH51" s="60"/>
+      <c r="AI51" s="60"/>
+      <c r="AK51" s="60"/>
+      <c r="AL51" s="60"/>
+      <c r="AM51" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="AN51" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="AO51" s="60"/>
+      <c r="AP51" s="60"/>
+      <c r="AQ51" s="60"/>
+      <c r="AR51" s="60"/>
+      <c r="AS51" s="60"/>
+      <c r="AT51" s="60"/>
+      <c r="AU51" s="60"/>
+      <c r="AW51" s="60"/>
+      <c r="AX51" s="60"/>
+      <c r="BA51"/>
+    </row>
+    <row r="52" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B52" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="C52" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="O52" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="P52" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q52" s="60"/>
+      <c r="R52" s="60"/>
+      <c r="S52" s="60"/>
+      <c r="T52" s="60"/>
+      <c r="U52" s="60"/>
+      <c r="V52" s="60"/>
+      <c r="W52" s="60"/>
+      <c r="Y52" s="60"/>
+      <c r="Z52" s="60"/>
+      <c r="AA52" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="AB52" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="AC52" s="60"/>
+      <c r="AD52" s="60"/>
+      <c r="AE52" s="60"/>
+      <c r="AF52" s="60"/>
+      <c r="AG52" s="60"/>
+      <c r="AH52" s="60"/>
+      <c r="AI52" s="60"/>
+      <c r="AK52" s="60"/>
+      <c r="AL52" s="60"/>
+      <c r="AM52" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="AN52" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="AO52" s="60"/>
+      <c r="AP52" s="60"/>
+      <c r="AQ52" s="60"/>
+      <c r="AR52" s="60"/>
+      <c r="AS52" s="60"/>
+      <c r="AT52" s="60"/>
+      <c r="AU52" s="60"/>
+      <c r="AW52" s="60"/>
+      <c r="AX52" s="60"/>
+      <c r="BA52"/>
+    </row>
+    <row r="53" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B53" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="C53" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="O53" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="P53" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q53" s="60"/>
+      <c r="R53" s="60"/>
+      <c r="S53" s="60"/>
+      <c r="T53" s="60"/>
+      <c r="U53" s="60"/>
+      <c r="V53" s="60"/>
+      <c r="W53" s="60"/>
+      <c r="Y53" s="60"/>
+      <c r="Z53" s="60"/>
+      <c r="AA53" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="AB53" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="AC53" s="60"/>
+      <c r="AD53" s="60"/>
+      <c r="AE53" s="60"/>
+      <c r="AF53" s="60"/>
+      <c r="AG53" s="60"/>
+      <c r="AH53" s="60"/>
+      <c r="AI53" s="60"/>
+      <c r="AK53" s="60"/>
+      <c r="AL53" s="60"/>
+      <c r="AM53" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="AN53" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="AO53" s="60"/>
+      <c r="AP53" s="60"/>
+      <c r="AQ53" s="60"/>
+      <c r="AR53" s="60"/>
+      <c r="AS53" s="60"/>
+      <c r="AT53" s="60"/>
+      <c r="AU53" s="60"/>
+      <c r="AW53" s="60"/>
+      <c r="AX53" s="60"/>
+      <c r="BA53"/>
+    </row>
+    <row r="54" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B54" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="C54" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="O54" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P54" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q54" s="60"/>
+      <c r="R54" s="60"/>
+      <c r="S54" s="60"/>
+      <c r="T54" s="60"/>
+      <c r="U54" s="60"/>
+      <c r="V54" s="60"/>
+      <c r="W54" s="60"/>
+      <c r="Y54" s="60"/>
+      <c r="Z54" s="60"/>
+      <c r="AA54" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="AB54" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="AC54" s="60"/>
+      <c r="AD54" s="60"/>
+      <c r="AE54" s="60"/>
+      <c r="AF54" s="60"/>
+      <c r="AG54" s="60"/>
+      <c r="AH54" s="60"/>
+      <c r="AI54" s="60"/>
+      <c r="AK54" s="60"/>
+      <c r="AL54" s="60"/>
+      <c r="AM54" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="AN54" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AO54" s="60"/>
+      <c r="AP54" s="60"/>
+      <c r="AQ54" s="60"/>
+      <c r="AR54" s="60"/>
+      <c r="AS54" s="60"/>
+      <c r="AT54" s="60"/>
+      <c r="AU54" s="60"/>
+      <c r="AW54" s="60"/>
+      <c r="AX54" s="60"/>
+      <c r="BA54"/>
+    </row>
+    <row r="55" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B55" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C55" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="O55" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="P55" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q55" s="60"/>
+      <c r="R55" s="60"/>
+      <c r="S55" s="60"/>
+      <c r="T55" s="60"/>
+      <c r="U55" s="60"/>
+      <c r="V55" s="60"/>
+      <c r="W55" s="60"/>
+      <c r="Y55" s="60"/>
+      <c r="Z55" s="60"/>
+      <c r="AA55" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="AB55" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="AC55" s="60"/>
+      <c r="AD55" s="60"/>
+      <c r="AE55" s="60"/>
+      <c r="AF55" s="60"/>
+      <c r="AG55" s="60"/>
+      <c r="AH55" s="60"/>
+      <c r="AI55" s="60"/>
+      <c r="AK55" s="60"/>
+      <c r="AL55" s="60"/>
+      <c r="AM55" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="AN55" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AO55" s="60"/>
+      <c r="AP55" s="60"/>
+      <c r="AQ55" s="60"/>
+      <c r="AR55" s="60"/>
+      <c r="AS55" s="60"/>
+      <c r="AT55" s="60"/>
+      <c r="AU55" s="60"/>
+      <c r="AW55" s="60"/>
+      <c r="AX55" s="60"/>
+      <c r="BA55"/>
+    </row>
+    <row r="56" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B56" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C56" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="O56" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="P56" s="86" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q56" s="60"/>
+      <c r="R56" s="60"/>
+      <c r="S56" s="60"/>
+      <c r="T56" s="60"/>
+      <c r="U56" s="60"/>
+      <c r="V56" s="60"/>
+      <c r="W56" s="60"/>
+      <c r="Y56" s="60"/>
+      <c r="Z56" s="60"/>
+      <c r="AA56" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="AB56" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="AC56" s="60"/>
+      <c r="AD56" s="60"/>
+      <c r="AE56" s="60"/>
+      <c r="AF56" s="60"/>
+      <c r="AG56" s="60"/>
+      <c r="AH56" s="60"/>
+      <c r="AI56" s="60"/>
+      <c r="AK56" s="60"/>
+      <c r="AL56" s="60"/>
+      <c r="AM56" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="AN56" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AQ56" s="60"/>
+      <c r="AR56" s="60"/>
+      <c r="AS56" s="60"/>
+      <c r="AT56" s="60"/>
+      <c r="AU56" s="60"/>
+      <c r="AW56" s="60"/>
+      <c r="AX56" s="60"/>
+      <c r="BA56"/>
+    </row>
+    <row r="57" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B57" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="C57" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="O57" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="P57" s="86" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA57" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="AB57" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="AC57" s="60"/>
+      <c r="AD57" s="60"/>
+      <c r="AE57" s="60"/>
+      <c r="AF57" s="60"/>
+      <c r="AG57" s="60"/>
+      <c r="AH57" s="60"/>
+      <c r="AI57" s="60"/>
+      <c r="AK57" s="60"/>
+      <c r="AL57" s="60"/>
+      <c r="AM57" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="AN57" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AQ57" s="60"/>
+      <c r="AR57" s="60"/>
+      <c r="AS57" s="60"/>
+      <c r="AT57" s="60"/>
+      <c r="AU57" s="60"/>
+      <c r="AW57" s="60"/>
+      <c r="AX57" s="60"/>
+      <c r="BA57"/>
+    </row>
+    <row r="58" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B58" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="C58" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="O58" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="P58" s="86" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA58" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB58" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AC58" s="60"/>
+      <c r="AF58" s="60"/>
+      <c r="AG58" s="60"/>
+      <c r="AH58" s="60"/>
+      <c r="AI58" s="60"/>
+      <c r="AK58" s="60"/>
+      <c r="AL58" s="60"/>
+      <c r="AM58" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="AN58" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AQ58" s="60"/>
+      <c r="AR58" s="60"/>
+      <c r="AS58" s="60"/>
+      <c r="AT58" s="60"/>
+      <c r="AU58" s="60"/>
+      <c r="AW58" s="60"/>
+      <c r="AX58" s="60"/>
+      <c r="BA58"/>
+    </row>
+    <row r="59" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B59" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O59" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="P59" s="59" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA59" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB59" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AC59" s="60"/>
+      <c r="AF59" s="60"/>
+      <c r="AG59" s="60"/>
+      <c r="AH59" s="60"/>
+      <c r="AI59" s="60"/>
+      <c r="AK59" s="60"/>
+      <c r="AL59" s="60"/>
+      <c r="AM59" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="AN59" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AO59" s="60"/>
+      <c r="AP59" s="60"/>
+      <c r="AQ59" s="60"/>
+      <c r="AR59" s="60"/>
+      <c r="AS59" s="60"/>
+      <c r="AT59" s="60"/>
+      <c r="AU59" s="60"/>
+      <c r="AW59" s="60"/>
+      <c r="AX59" s="60"/>
+      <c r="BA59"/>
+    </row>
+    <row r="60" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B60" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O60" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="P60" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AA60" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="AB60" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AC60" s="60"/>
+      <c r="AF60" s="60"/>
+      <c r="AG60" s="60"/>
+      <c r="AH60" s="60"/>
+      <c r="AI60" s="60"/>
+      <c r="AK60" s="60"/>
+      <c r="AL60" s="60"/>
+      <c r="AM60" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="AN60" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AO60" s="60"/>
+      <c r="AP60" s="60"/>
+      <c r="AQ60" s="60"/>
+      <c r="AR60" s="60"/>
+      <c r="AS60" s="60"/>
+      <c r="AT60" s="60"/>
+      <c r="AU60" s="60"/>
+      <c r="AW60" s="60"/>
+      <c r="AX60" s="60"/>
+      <c r="BA60"/>
+    </row>
+    <row r="61" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B61" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O61" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="P61" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AA61" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="AB61" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AC61" s="60"/>
+      <c r="AD61" s="60"/>
+      <c r="AE61" s="60"/>
+      <c r="AF61" s="60"/>
+      <c r="AG61" s="60"/>
+      <c r="AH61" s="60"/>
+      <c r="AI61" s="60"/>
+      <c r="AK61" s="60"/>
+      <c r="AL61" s="60"/>
+      <c r="AM61" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="AN61" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AO61" s="60"/>
+      <c r="AP61" s="60"/>
+      <c r="AQ61" s="60"/>
+      <c r="AR61" s="60"/>
+      <c r="AS61" s="60"/>
+      <c r="AT61" s="60"/>
+      <c r="AU61" s="60"/>
+      <c r="AW61" s="60"/>
+      <c r="AX61" s="60"/>
+      <c r="BA61"/>
+    </row>
+    <row r="62" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B62" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O62" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="P62" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AA62" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB62" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AC62" s="60"/>
+      <c r="AD62" s="60"/>
+      <c r="AE62" s="60"/>
+      <c r="AF62" s="60"/>
+      <c r="AG62" s="60"/>
+      <c r="AH62" s="60"/>
+      <c r="AI62" s="60"/>
+      <c r="AK62" s="60"/>
+      <c r="AL62" s="60"/>
+      <c r="AM62" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="AN62" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO62" s="60"/>
+      <c r="AP62" s="60"/>
+      <c r="AQ62" s="60"/>
+      <c r="AR62" s="60"/>
+      <c r="AS62" s="60"/>
+      <c r="AT62" s="60"/>
+      <c r="AU62" s="60"/>
+      <c r="AW62" s="60"/>
+      <c r="AX62" s="60"/>
+      <c r="BA62"/>
+    </row>
+    <row r="63" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B63" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O63" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="P63" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AA63" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="AB63" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AC63" s="60"/>
+      <c r="AD63" s="60"/>
+      <c r="AE63" s="60"/>
+      <c r="AF63" s="60"/>
+      <c r="AG63" s="60"/>
+      <c r="AH63" s="60"/>
+      <c r="AI63" s="60"/>
+      <c r="AK63" s="60"/>
+      <c r="AL63" s="60"/>
+      <c r="AM63" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="AN63" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO63" s="60"/>
+      <c r="AP63" s="60"/>
+      <c r="AQ63" s="60"/>
+      <c r="AR63" s="60"/>
+      <c r="AS63" s="60"/>
+      <c r="AT63" s="60"/>
+      <c r="AU63" s="60"/>
+      <c r="AW63" s="60"/>
+      <c r="AX63" s="60"/>
+      <c r="BA63"/>
+    </row>
+    <row r="64" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B64" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O64" s="14" t="s">
+        <v>402</v>
+      </c>
+      <c r="P64" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AA64" s="89" t="s">
+        <v>416</v>
+      </c>
+      <c r="AB64" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="AC64" s="60"/>
+      <c r="AD64" s="60"/>
+      <c r="AE64" s="60"/>
+      <c r="AF64" s="60"/>
+      <c r="AG64" s="60"/>
+      <c r="AH64" s="60"/>
+      <c r="AI64" s="60"/>
+      <c r="AK64" s="60"/>
+      <c r="AL64" s="60"/>
+      <c r="AM64" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="AN64" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO64" s="60"/>
+      <c r="AP64" s="60"/>
+      <c r="AQ64" s="60"/>
+      <c r="AR64" s="60"/>
+      <c r="AS64" s="60"/>
+      <c r="AT64" s="60"/>
+      <c r="AU64" s="60"/>
+      <c r="AW64" s="60"/>
+      <c r="AX64" s="60"/>
+      <c r="BA64"/>
+    </row>
+    <row r="65" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B65" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O65" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="P65" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q65" s="60"/>
+      <c r="R65" s="60"/>
+      <c r="S65" s="60"/>
+      <c r="T65" s="60"/>
+      <c r="U65" s="60"/>
+      <c r="V65" s="60"/>
+      <c r="W65" s="60"/>
+      <c r="Y65" s="60"/>
+      <c r="Z65" s="60"/>
+      <c r="AA65" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="AB65" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC65" s="60"/>
+      <c r="AD65" s="60"/>
+      <c r="AE65" s="60"/>
+      <c r="AF65" s="60"/>
+      <c r="AG65" s="60"/>
+      <c r="AH65" s="60"/>
+      <c r="AI65" s="60"/>
+      <c r="AK65" s="60"/>
+      <c r="AL65" s="60"/>
+      <c r="AM65" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="AN65" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO65" s="60"/>
+      <c r="AP65" s="60"/>
+      <c r="AQ65" s="60"/>
+      <c r="AR65" s="60"/>
+      <c r="AS65" s="60"/>
+      <c r="AT65" s="60"/>
+      <c r="AU65" s="60"/>
+      <c r="AW65" s="60"/>
+      <c r="AX65" s="60"/>
+      <c r="BA65"/>
+    </row>
+    <row r="66" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B66" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O66" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="P66" s="84" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q66" s="60"/>
+      <c r="R66" s="60"/>
+      <c r="S66" s="60"/>
+      <c r="T66" s="60"/>
+      <c r="U66" s="60"/>
+      <c r="V66" s="60"/>
+      <c r="W66" s="60"/>
+      <c r="Y66" s="60"/>
+      <c r="Z66" s="60"/>
+      <c r="AA66" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="AB66" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC66" s="60"/>
+      <c r="AD66" s="60"/>
+      <c r="AE66" s="60"/>
+      <c r="AF66" s="60"/>
+      <c r="AG66" s="60"/>
+      <c r="AH66" s="60"/>
+      <c r="AI66" s="60"/>
+      <c r="AK66" s="60"/>
+      <c r="AL66" s="60"/>
+      <c r="AM66" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="AN66" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO66" s="60"/>
+      <c r="AP66" s="60"/>
+      <c r="AQ66" s="60"/>
+      <c r="AR66" s="60"/>
+      <c r="AS66" s="60"/>
+      <c r="AT66" s="60"/>
+      <c r="AU66" s="60"/>
+      <c r="AW66" s="60"/>
+      <c r="AX66" s="60"/>
+      <c r="BA66"/>
+    </row>
+    <row r="67" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B67" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="C67" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="O67" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="P67" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q67" s="60"/>
+      <c r="R67" s="60"/>
+      <c r="S67" s="60"/>
+      <c r="T67" s="60"/>
+      <c r="U67" s="60"/>
+      <c r="V67" s="60"/>
+      <c r="W67" s="60"/>
+      <c r="Y67" s="60"/>
+      <c r="Z67" s="60"/>
+      <c r="AA67" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="AB67" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC67" s="60"/>
+      <c r="AD67" s="60"/>
+      <c r="AE67" s="60"/>
+      <c r="AF67" s="60"/>
+      <c r="AG67" s="60"/>
+      <c r="AH67" s="60"/>
+      <c r="AI67" s="60"/>
+      <c r="AK67" s="60"/>
+      <c r="AL67" s="60"/>
+      <c r="AM67" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="AN67" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO67" s="60"/>
+      <c r="AP67" s="60"/>
+      <c r="AQ67" s="60"/>
+      <c r="AR67" s="60"/>
+      <c r="AS67" s="60"/>
+      <c r="AT67" s="60"/>
+      <c r="AU67" s="60"/>
+      <c r="AW67" s="60"/>
+      <c r="AX67" s="60"/>
+      <c r="BA67"/>
+    </row>
+    <row r="68" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B68" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="C68" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="O68" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="P68" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q68" s="60"/>
+      <c r="R68" s="60"/>
+      <c r="S68" s="60"/>
+      <c r="T68" s="60"/>
+      <c r="U68" s="60"/>
+      <c r="V68" s="60"/>
+      <c r="W68" s="60"/>
+      <c r="Y68" s="60"/>
+      <c r="Z68" s="60"/>
+      <c r="AA68" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="AB68" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC68" s="60"/>
+      <c r="AD68" s="60"/>
+      <c r="AE68" s="60"/>
+      <c r="AF68" s="60"/>
+      <c r="AG68" s="60"/>
+      <c r="AH68" s="60"/>
+      <c r="AI68" s="60"/>
+      <c r="AK68" s="60"/>
+      <c r="AL68" s="60"/>
+      <c r="AM68" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="AN68" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO68" s="60"/>
+      <c r="AP68" s="60"/>
+      <c r="AQ68" s="60"/>
+      <c r="AR68" s="60"/>
+      <c r="AS68" s="60"/>
+      <c r="AT68" s="60"/>
+      <c r="AU68" s="60"/>
+      <c r="AW68" s="60"/>
+      <c r="AX68" s="60"/>
+      <c r="BA68"/>
+    </row>
+    <row r="69" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B69" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="C69" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="O69" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="P69" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q69" s="60"/>
+      <c r="R69" s="60"/>
+      <c r="S69" s="60"/>
+      <c r="T69" s="60"/>
+      <c r="U69" s="60"/>
+      <c r="V69" s="60"/>
+      <c r="W69" s="60"/>
+      <c r="Y69" s="60"/>
+      <c r="Z69" s="60"/>
+      <c r="AA69" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="AB69" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC69" s="60"/>
+      <c r="AD69" s="60"/>
+      <c r="AE69" s="60"/>
+      <c r="AF69" s="60"/>
+      <c r="AG69" s="60"/>
+      <c r="AH69" s="60"/>
+      <c r="AI69" s="60"/>
+      <c r="AK69" s="60"/>
+      <c r="AL69" s="60"/>
+      <c r="AM69" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="AN69" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO69" s="60"/>
+      <c r="AP69" s="60"/>
+      <c r="AQ69" s="60"/>
+      <c r="AR69" s="60"/>
+      <c r="AS69" s="60"/>
+      <c r="AT69" s="60"/>
+      <c r="AU69" s="60"/>
+      <c r="AW69" s="60"/>
+      <c r="AX69" s="60"/>
+      <c r="BA69"/>
+    </row>
+    <row r="70" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B70" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="C70" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="O70" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="P70" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q70" s="60"/>
+      <c r="R70" s="60"/>
+      <c r="S70" s="60"/>
+      <c r="T70" s="60"/>
+      <c r="U70" s="60"/>
+      <c r="V70" s="60"/>
+      <c r="W70" s="60"/>
+      <c r="Y70" s="60"/>
+      <c r="Z70" s="60"/>
+      <c r="AA70" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="AB70" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC70" s="60"/>
+      <c r="AD70" s="60"/>
+      <c r="AE70" s="60"/>
+      <c r="AF70" s="60"/>
+      <c r="AG70" s="60"/>
+      <c r="AH70" s="60"/>
+      <c r="AI70" s="60"/>
+      <c r="AK70" s="60"/>
+      <c r="AL70" s="60"/>
+      <c r="AM70" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="AN70" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO70" s="60"/>
+      <c r="AP70" s="60"/>
+      <c r="AQ70" s="60"/>
+      <c r="AR70" s="60"/>
+      <c r="AS70" s="60"/>
+      <c r="AT70" s="60"/>
+      <c r="AU70" s="60"/>
+      <c r="AW70" s="60"/>
+      <c r="AX70" s="60"/>
+      <c r="BA70"/>
+    </row>
+    <row r="71" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B71" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="C71" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="O71" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="P71" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q71" s="60"/>
+      <c r="R71" s="60"/>
+      <c r="S71" s="60"/>
+      <c r="T71" s="60"/>
+      <c r="U71" s="60"/>
+      <c r="V71" s="60"/>
+      <c r="W71" s="60"/>
+      <c r="Y71" s="60"/>
+      <c r="Z71" s="60"/>
+      <c r="AA71" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="AB71" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC71" s="60"/>
+      <c r="AD71" s="60"/>
+      <c r="AE71" s="60"/>
+      <c r="AF71" s="60"/>
+      <c r="AG71" s="60"/>
+      <c r="AH71" s="60"/>
+      <c r="AI71" s="60"/>
+      <c r="AK71" s="60"/>
+      <c r="AL71" s="60"/>
+      <c r="AM71" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="AN71" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AO71" s="60"/>
+      <c r="AP71" s="60"/>
+      <c r="AQ71" s="60"/>
+      <c r="AR71" s="60"/>
+      <c r="AS71" s="60"/>
+      <c r="AT71" s="60"/>
+      <c r="AU71" s="60"/>
+      <c r="AW71" s="60"/>
+      <c r="AX71" s="60"/>
+      <c r="BA71"/>
+    </row>
+    <row r="72" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B72" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="C72" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="O72" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="P72" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q72" s="60"/>
+      <c r="R72" s="60"/>
+      <c r="S72" s="60"/>
+      <c r="T72" s="60"/>
+      <c r="U72" s="60"/>
+      <c r="V72" s="60"/>
+      <c r="W72" s="60"/>
+      <c r="Y72" s="60"/>
+      <c r="Z72" s="60"/>
+      <c r="AA72" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="AB72" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC72" s="60"/>
+      <c r="AD72" s="60"/>
+      <c r="AE72" s="60"/>
+      <c r="AF72" s="60"/>
+      <c r="AG72" s="60"/>
+      <c r="AH72" s="60"/>
+      <c r="AI72" s="60"/>
+      <c r="AK72" s="60"/>
+      <c r="AL72" s="60"/>
+      <c r="AM72" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="AN72" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AO72" s="60"/>
+      <c r="AP72" s="60"/>
+      <c r="AQ72" s="60"/>
+      <c r="AR72" s="60"/>
+      <c r="AS72" s="60"/>
+      <c r="AT72" s="60"/>
+      <c r="AU72" s="60"/>
+      <c r="AW72" s="60"/>
+      <c r="AX72" s="60"/>
+      <c r="BA72"/>
+    </row>
+    <row r="73" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B73" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="C73" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="O73" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="P73" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA73" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="AB73" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC73" s="60"/>
+      <c r="AD73" s="60"/>
+      <c r="AE73" s="60"/>
+      <c r="AF73" s="60"/>
+      <c r="AG73" s="60"/>
+      <c r="AH73" s="60"/>
+      <c r="AI73" s="60"/>
+      <c r="AK73" s="60"/>
+      <c r="AL73" s="60"/>
+      <c r="AM73" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="AN73" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AO73" s="60"/>
+      <c r="AP73" s="60"/>
+      <c r="AQ73" s="60"/>
+      <c r="AR73" s="60"/>
+      <c r="AS73" s="60"/>
+      <c r="AT73" s="60"/>
+      <c r="AU73" s="60"/>
+      <c r="AW73" s="60"/>
+      <c r="AX73" s="60"/>
+      <c r="BA73"/>
+    </row>
+    <row r="74" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="B74" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="C74" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="O74" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="P74" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA74" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="AB74" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM74" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="AN74" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="BA74"/>
+    </row>
+    <row r="75" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="O75" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="P75" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA75" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="AB75" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM75" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="AN75" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="BA75"/>
+    </row>
+    <row r="76" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="O76" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="P76" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA76" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="AB76" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM76" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="AN76" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="BA76"/>
+    </row>
+    <row r="77" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="O77" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="P77" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA77" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="AB77" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM77" s="14" t="s">
+        <v>389</v>
+      </c>
+      <c r="AN77" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="BA77"/>
+    </row>
+    <row r="78" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="O78" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="P78" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA78" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="AB78" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="BA78"/>
+    </row>
+    <row r="79" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="O79" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="P79" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA79" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="AB79" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="BA79"/>
+    </row>
+    <row r="80" spans="2:53" x14ac:dyDescent="0.25">
+      <c r="O80" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="P80" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA80" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="AB80" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="BA80"/>
+    </row>
+    <row r="81" spans="15:53" x14ac:dyDescent="0.25">
+      <c r="O81" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="P81" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA81" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="AB81" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="BA81"/>
+    </row>
+    <row r="82" spans="15:53" x14ac:dyDescent="0.25">
+      <c r="O82" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="P82" s="53" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AM2:AN2"/>
+    <mergeCell ref="AZ2:BA2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Count.xlsx
+++ b/Count.xlsx
@@ -2042,34 +2042,34 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
